--- a/Comentarios Campaña.xlsx
+++ b/Comentarios Campaña.xlsx
@@ -19,11 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -54,10 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -423,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,6 +501,11 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>extraction_status</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>created_time_raw</t>
         </is>
       </c>
@@ -545,7 +547,7 @@
       <c r="H2" s="1" t="n">
         <v>46211.58980324074</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="I2" s="1" t="n">
         <v>46211</v>
       </c>
       <c r="J2" t="inlineStr">
@@ -568,7 +570,8 @@
           <t>https://instagram.com/mat18545</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>{'postUrl': 'https://www.instagram.com/p/DZ5yxYgAy5c/', 'commentUrl': 'https://www.instagram.com/p/DZ5yxYgAy5c/c/18197756167366742', 'id': '18197756167366742', 'text': 'Vuelvan a los animales marinos por favor', 'ownerUsername': 'mat18545', 'ownerProfilePicUrl': 'https://scontent-bru2-1.cdninstagram.com/v/t51.2885-19/469370398_1109721463381756_4068535561865210393_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=103&amp;ig_cache_key=GB4G_hv83p8pSfEDABkqBZmJV3Y4bkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;</t>
         </is>
@@ -611,7 +614,7 @@
       <c r="H3" s="1" t="n">
         <v>46210.59957175926</v>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="I3" s="1" t="n">
         <v>46210</v>
       </c>
       <c r="J3" t="inlineStr">
@@ -634,7 +637,8 @@
           <t>https://instagram.com/sleepy_dunez</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>{'postUrl': 'https://www.instagram.com/p/DZ5yxYgAy5c/', 'commentUrl': 'https://www.instagram.com/p/DZ5yxYgAy5c/c/17985727140032292', 'id': '17985727140032292', 'text': 'Creo que le deberían cambiar el nombre😭🥀', 'ownerUsername': 'sleepy_dunez', 'ownerProfilePicUrl': 'https://scontent-bru2-1.cdninstagram.com/v/t51.82787-19/726373129_17888033775561289_5001866020940776711_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=110&amp;ig_cache_key=GAmTSytJKuxqEo0-AAeFRSClMmpFbmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=6</t>
         </is>
@@ -673,7 +677,7 @@
       <c r="H4" s="1" t="n">
         <v>46224.8952199074</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="I4" s="1" t="n">
         <v>46224</v>
       </c>
       <c r="J4" t="inlineStr">
@@ -681,10 +685,8 @@
           <t>21:29:07</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K4" t="n">
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -694,7 +696,8 @@
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02udMVuBcdbK41WvjByhYEQaUDdeSnJEYra5pbSmbpFE35xNrfEPjqpcp5fYfvapznl?comment_id=1726957944992593', 'commentId': '1726957944992593', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE3MjY5NTc5NDQ5OTI1OTM=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNzI2OTU3OTQ0OTkyNTkz', 'date': '2026-07-21T21:29:07.000</t>
         </is>
@@ -733,7 +736,7 @@
       <c r="H5" s="1" t="n">
         <v>46220.97578703704</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="I5" s="1" t="n">
         <v>46220</v>
       </c>
       <c r="J5" t="inlineStr">
@@ -741,10 +744,8 @@
           <t>23:25:08</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="K5" t="n">
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -754,7 +755,8 @@
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02udMVuBcdbK41WvjByhYEQaUDdeSnJEYra5pbSmbpFE35xNrfEPjqpcp5fYfvapznl?comment_id=1078533431788344', 'commentId': '1078533431788344', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzEwNzg1MzM0MzE3ODgzNDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xMDc4NTMzNDMxNzg4MzQ0', 'date': '2026-07-17T23:25:08.000</t>
         </is>
@@ -793,7 +795,7 @@
       <c r="H6" s="1" t="n">
         <v>46224.97891203704</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="I6" s="1" t="n">
         <v>46224</v>
       </c>
       <c r="J6" t="inlineStr">
@@ -801,10 +803,8 @@
           <t>23:29:38</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K6" t="n">
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -814,7 +814,8 @@
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0318dHUiAt3TwtwBAG5K5RTrhvnhqyxZ8twzrn5cnNuYKUiFWwMrvQuCQSuZRsMYpl?comment_id=1037649185543740', 'commentId': '1037649185543740', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEwMzc2NDkxODU1NDM3NDA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMDM3NjQ5MTg1NTQzNzQw', 'date': '2026-07-21T23:29:38.000Z'</t>
         </is>
@@ -853,7 +854,7 @@
       <c r="H7" s="1" t="n">
         <v>46223.08563657408</v>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="I7" s="1" t="n">
         <v>46223</v>
       </c>
       <c r="J7" t="inlineStr">
@@ -861,10 +862,8 @@
           <t>02:03:19</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K7" t="n">
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -874,7 +873,8 @@
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0318dHUiAt3TwtwBAG5K5RTrhvnhqyxZ8twzrn5cnNuYKUiFWwMrvQuCQSuZRsMYpl?comment_id=1715884343017970', 'commentId': '1715884343017970', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3MTU4ODQzNDMwMTc5NzA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzE1ODg0MzQzMDE3OTcw', 'date': '2026-07-20T02:03:19.000Z'</t>
         </is>
@@ -913,7 +913,7 @@
       <c r="H8" s="1" t="n">
         <v>46217.89942129629</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I8" s="1" t="n">
         <v>46217</v>
       </c>
       <c r="J8" t="inlineStr">
@@ -921,10 +921,8 @@
           <t>21:35:10</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K8" t="n">
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -934,7 +932,8 @@
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0318dHUiAt3TwtwBAG5K5RTrhvnhqyxZ8twzrn5cnNuYKUiFWwMrvQuCQSuZRsMYpl?comment_id=1296257932579939', 'commentId': '1296257932579939', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEyOTYyNTc5MzI1Nzk5Mzk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMjk2MjU3OTMyNTc5OTM5', 'date': '2026-07-14T21:35:10.000Z'</t>
         </is>
@@ -973,7 +972,7 @@
       <c r="H9" s="1" t="n">
         <v>46221.04325231481</v>
       </c>
-      <c r="I9" s="2" t="n">
+      <c r="I9" s="1" t="n">
         <v>46221</v>
       </c>
       <c r="J9" t="inlineStr">
@@ -981,10 +980,8 @@
           <t>01:02:17</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K9" t="n">
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -994,7 +991,8 @@
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0PPzCSaFA3zFkaWC8poSXA2EYQuRYnwkjoyLTprPy1r9m2BeiDzFs4vhuxfYak5SUl?comment_id=2000809543966891', 'commentId': '2000809543966891', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzIwMDA4MDk1NDM5NjY4OTE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8yMDAwODA5NTQzOTY2ODkx', 'date': '2026-07-18T01:02:17.000Z</t>
         </is>
@@ -1033,7 +1031,7 @@
       <c r="H10" s="1" t="n">
         <v>46221.10013888889</v>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="I10" s="1" t="n">
         <v>46221</v>
       </c>
       <c r="J10" t="inlineStr">
@@ -1041,10 +1039,8 @@
           <t>02:24:12</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K10" t="n">
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1054,7 +1050,8 @@
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02nLVXgTHGwmggpBe5faHYc89sSnUpgEdjRFbk5NGY5KGH4PAWPpuk1w7uxjkEhy3ul?comment_id=1570496154770550', 'commentId': '1570496154770550', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NzA0OTYxNTQ3NzA1NTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTcwNDk2MTU0NzcwNTUw', 'date': '2026-07-18T02:24:12.000</t>
         </is>
@@ -1093,7 +1090,7 @@
       <c r="H11" s="1" t="n">
         <v>46221.00662037037</v>
       </c>
-      <c r="I11" s="2" t="n">
+      <c r="I11" s="1" t="n">
         <v>46221</v>
       </c>
       <c r="J11" t="inlineStr">
@@ -1101,10 +1098,8 @@
           <t>00:09:32</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K11" t="n">
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1114,7 +1109,8 @@
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02nLVXgTHGwmggpBe5faHYc89sSnUpgEdjRFbk5NGY5KGH4PAWPpuk1w7uxjkEhy3ul?comment_id=2061225511435404', 'commentId': '2061225511435404', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzIwNjEyMjU1MTE0MzU0MDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8yMDYxMjI1NTExNDM1NDA0', 'date': '2026-07-18T00:09:32.000</t>
         </is>
@@ -1153,7 +1149,7 @@
       <c r="H12" s="1" t="n">
         <v>46219.06762731481</v>
       </c>
-      <c r="I12" s="2" t="n">
+      <c r="I12" s="1" t="n">
         <v>46219</v>
       </c>
       <c r="J12" t="inlineStr">
@@ -1161,10 +1157,8 @@
           <t>01:37:23</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K12" t="n">
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1174,7 +1168,8 @@
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02nLVXgTHGwmggpBe5faHYc89sSnUpgEdjRFbk5NGY5KGH4PAWPpuk1w7uxjkEhy3ul?comment_id=1554955609342819', 'commentId': '1554955609342819', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NTQ5NTU2MDkzNDI4MTk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTU0OTU1NjA5MzQyODE5', 'date': '2026-07-16T01:37:23.000</t>
         </is>

--- a/Comentarios Campaña.xlsx
+++ b/Comentarios Campaña.xlsx
@@ -19,9 +19,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -52,9 +54,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1172,6 +1175,4469 @@
       <c r="Q12" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02nLVXgTHGwmggpBe5faHYc89sSnUpgEdjRFbk5NGY5KGH4PAWPpuk1w7uxjkEhy3ul?comment_id=1554955609342819', 'commentId': '1554955609342819', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NTQ5NTU2MDkzNDI4MTk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTU0OTU1NjA5MzQyODE5', 'date': '2026-07-16T01:37:23.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>bolaochoradio_jlm</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>❤️❤️❤️👏👏👏</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-06-12T14:07:28.000Z</t>
+        </is>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>46185.58851851852</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>14:07:28</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="b">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>https://instagram.com/bolaochoradio_jlm</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/18028010735820663', 'id': '18028010735820663', 'text': '❤️❤️❤️👏👏👏', 'ownerUsername': 'bolaochoradio_jlm', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.82787-19/609426657_18278152333304341_7731619025179557966_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=106&amp;ig_cache_key=GOEcUyQVIvr44e9AAE7Aeh6KOkxrbmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3Rh</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>anmeyrojasguerrero</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Como así que descontinuaron el alpin de vainilla ??</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-06-07T18:12:49.000Z</t>
+        </is>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>46180.75890046296</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>46180</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>18:12:49</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="b">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>https://instagram.com/anmeyrojasguerrero</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/18115431067869225', 'id': '18115431067869225', 'text': 'Como así que descontinuaron el alpin de vainilla ??', 'ownerUsername': 'anmeyrojasguerrero', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.82787-19/747452351_18188931100388565_1874264507433900028_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=107&amp;ig_cache_key=GL83jSzVLBWJvJ5AAPxXuKSjuQIabmNDAQAB1501500j-ccb7-5&amp;</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>lauraveronica_er</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>@sinergiaanimalcolombia</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-06-03T05:37:44.000Z</t>
+        </is>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>46176.23453703704</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>05:37:44</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="b">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>https://instagram.com/lauraveronica_er</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/17898759165309051', 'id': '17898759165309051', 'text': '@sinergiaanimalcolombia', 'ownerUsername': 'lauraveronica_er', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.2885-19/411363410_702264891880776_6971867694952727024_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=102&amp;cb=8438d1d6-89aba764&amp;ig_cache_key=GFLohBhINWvJtH4CAPDBreK6DMFgbkULAAAB1501500j-ccb7-5-cb8438d1d6-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>joujou0107</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Porque volvió el ruido que enloquece en la tienda alpina de la 79 .. parece que el@techo no solucionó el problema .. lo amplifico</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-06-03T01:40:32.000Z</t>
+        </is>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>46176.06981481481</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>01:40:32</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="b">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>https://instagram.com/joujou0107</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/18103828820045784', 'id': '18103828820045784', 'text': 'Porque volvió el ruido que enloquece en la tienda alpina de la 79 .. parece que el@techo no solucionó el problema .. lo amplifico', 'ownerUsername': 'joujou0107', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.2885-19/372932570_1962546517445924_7694878205033810064_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>yosoy_j_e_r_</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Un año mas de explotación animal 🥰</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-06-02T21:00:24.000Z</t>
+        </is>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>46175.87527777778</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>46175</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>21:00:24</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="b">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>https://instagram.com/yosoy_j_e_r_</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/18122781676709889', 'id': '18122781676709889', 'text': 'Un año mas de explotación animal 🥰', 'ownerUsername': 'yosoy_j_e_r_', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.82787-19/619396999_18387138832147571_3896305389898522995_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=104&amp;ig_cache_key=GIc-6yRzpIZeAVNBAHNhV80bdRI2bmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>6</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>lauraveronica_er</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>@yosoy_j_e_r_</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:54:35.000Z</t>
+        </is>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>46175.78790509259</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>46175</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>18:54:35</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="b">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>https://instagram.com/lauraveronica_er</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/18053058014750981', 'id': '18053058014750981', 'text': '@yosoy_j_e_r_', 'ownerUsername': 'lauraveronica_er', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.2885-19/411363410_702264891880776_6971867694952727024_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=102&amp;cb=8438d1d6-89aba764&amp;ig_cache_key=GFLohBhINWvJtH4CAPDBreK6DMFgbkULAAAB1501500j-ccb7-5-cb8438d1d6-89aba764&amp;cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>6</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>lauraveronica_er</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Una vida sin leche sería hermosa! Una vida sin maltrato animal!</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:54:17.000Z</t>
+        </is>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>46175.78769675926</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>46175</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>18:54:17</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>https://instagram.com/lauraveronica_er</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/18142689715518670', 'id': '18142689715518670', 'text': 'Una vida sin leche sería hermosa! Una vida sin maltrato animal!', 'ownerUsername': 'lauraveronica_er', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.2885-19/411363410_702264891880776_6971867694952727024_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=102&amp;ig_cache_key=GFLohBhINWvJtH4CAPDBreK6DMFgbkULAAAB1501500j-</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>6</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>milefierro031</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Sin leche no hay vida🔥💙🐮</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-06-02T12:43:30.000Z</t>
+        </is>
+      </c>
+      <c r="H20" s="1" t="n">
+        <v>46175.53020833333</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>46175</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>12:43:30</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="b">
+        <v>0</v>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>https://instagram.com/milefierro031</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/18099626549328332', 'id': '18099626549328332', 'text': 'Sin leche no hay vida🔥💙🐮', 'ownerUsername': 'milefierro031', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.75761-19/506018127_17846179632500400_2172907525543103403_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GE85KR6wzpd9AWc-AKsLxcXhtycebvEnAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>6</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>nmoralesr</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>🥛🩵</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-06-02T01:29:06.000Z</t>
+        </is>
+      </c>
+      <c r="H21" s="1" t="n">
+        <v>46175.061875</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>46175</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>01:29:06</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="b">
+        <v>0</v>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>https://instagram.com/nmoralesr</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/18133633018562481', 'id': '18133633018562481', 'text': '🥛\U0001fa75', 'ownerUsername': 'nmoralesr', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.82787-19/729929448_18596148781024346_1134176551830756346_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GOjWgStahEhKGRFCAPobc5SQZ70PbmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6In</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>6</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>luisamaya.remote</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>🐮muuuuuuuuy cool</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-06-02T00:42:31.000Z</t>
+        </is>
+      </c>
+      <c r="H22" s="1" t="n">
+        <v>46175.02952546296</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>46175</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>00:42:31</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="b">
+        <v>0</v>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>https://instagram.com/luisamaya.remote</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/18071152436679388', 'id': '18071152436679388', 'text': '🐮muuuuuuuuy cool', 'ownerUsername': 'luisamaya.remote', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.2885-19/51573136_293663161262767_2574048044513230848_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;cb=8438d1d6-89aba764&amp;ig_cache_key=GJDxEgOvImnIFQsBAAAAAAAP27gjbkULAAAB1501500j-ccb7-5-cb8438d1d6-89aba764&amp;</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>kellys_loving</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Feliz día @alpina 😍</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-06-01T23:42:54.000Z</t>
+        </is>
+      </c>
+      <c r="H23" s="1" t="n">
+        <v>46174.988125</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>23:42:54</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="b">
+        <v>0</v>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>https://instagram.com/kellys_loving</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/18141486358464579', 'id': '18141486358464579', 'text': 'Feliz día @alpina 😍', 'ownerUsername': 'kellys_loving', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.2885-19/458543973_1237439730504604_639025001783379578_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=104&amp;cb=8438d1d6-89aba764&amp;ig_cache_key=GGXTVBucU5HjcWUEAHpG5HnaRd4IbkULAAAB1501500j-ccb7-5-cb8438d1d6-89aba764</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>mariaclaudiapico</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>💙💙💙💙</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-06-01T22:55:38.000Z</t>
+        </is>
+      </c>
+      <c r="H24" s="1" t="n">
+        <v>46174.95530092593</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>22:55:38</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="b">
+        <v>0</v>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>https://instagram.com/mariaclaudiapico</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/18090521612625817', 'id': '18090521612625817', 'text': '💙💙💙💙', 'ownerUsername': 'mariaclaudiapico', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.2885-19/476488792_640473678517415_5706999738040182288_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GFikZhynlBjmgUYCABDmIVcGVjNPbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>mari.sdlv</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Sin leche no habría felicidad !! 🥛💙 Feliz día Alpina 🥹</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-06-01T20:54:47.000Z</t>
+        </is>
+      </c>
+      <c r="H25" s="1" t="n">
+        <v>46174.87137731481</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>20:54:47</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>2</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="b">
+        <v>0</v>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>https://instagram.com/mari.sdlv</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/17875000764610500', 'id': '17875000764610500', 'text': 'Sin leche no habría felicidad !! 🥛💙 Feliz día Alpina 🥹', 'ownerUsername': 'mari.sdlv', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.82787-19/523013216_18050972795530937_5521465705616428750_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=104&amp;cb=8438d1d6-89aba764&amp;ig_cache_key=GGCMLB_57lOdQyFAAM7OxCbOL6BMbmNDAQAB1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>soysanticruz</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>🙌🙌</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-06-01T18:36:13.000Z</t>
+        </is>
+      </c>
+      <c r="H26" s="1" t="n">
+        <v>46174.77515046296</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>18:36:13</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="b">
+        <v>0</v>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>https://instagram.com/soysanticruz</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/18107498516473913', 'id': '18107498516473913', 'text': '🙌🙌', 'ownerUsername': 'soysanticruz', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.75761-19/504146061_18508816267036736_3085562163605248657_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=102&amp;cb=8438d1d6-89aba764&amp;ig_cache_key=GI2oDB5ASM_aq8FBAJGaE5ZwHtIqbvEnAQAB1501500j-ccb7-5-cb8438d1d6-89aba764&amp;ccb=7-5&amp;_nc_si</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>buentipo.global</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>🥛</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-06-01T18:31:09.000Z</t>
+        </is>
+      </c>
+      <c r="H27" s="1" t="n">
+        <v>46174.77163194444</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>18:31:09</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="b">
+        <v>0</v>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>https://instagram.com/buentipo.global</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/18103723295043425', 'id': '18103723295043425', 'text': '🥛', 'ownerUsername': 'buentipo.global', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.75761-19/502965801_18326550277203333_6666050328820338889_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=109&amp;cb=8438d1d6-89aba764&amp;ig_cache_key=GCmm_h2FJTt-5htBAMlQNrB0kYJcbvEnAQAB1501500j-ccb7-5-cb8438d1d6-89aba764&amp;ccb=7-5&amp;_nc_</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>sebasforeroarango</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>🥛🩵🫰🏻</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-06-01T18:26:25.000Z</t>
+        </is>
+      </c>
+      <c r="H28" s="1" t="n">
+        <v>46174.76834490741</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>18:26:25</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="b">
+        <v>0</v>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>https://instagram.com/sebasforeroarango</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/18091418609613636', 'id': '18091418609613636', 'text': '🥛\U0001fa75🫰🏻', 'ownerUsername': 'sebasforeroarango', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.82787-19/683746054_18589577845048358_5347870612495357067_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=106&amp;cb=8438d1d6-89aba764&amp;ig_cache_key=GAYjwSgmhPpfHwtCAItUieL8czdKbmNDAQAB1501500j-ccb7-5-cb8438d1d6-89aba76</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>angelacedeno</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>🥛🐮🐄🐮🐮🩵</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-06-01T17:28:34.000Z</t>
+        </is>
+      </c>
+      <c r="H29" s="1" t="n">
+        <v>46174.72817129629</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>17:28:34</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="b">
+        <v>0</v>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>https://instagram.com/angelacedeno</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/18331810513264757', 'id': '18331810513264757', 'text': '🥛🐮🐄🐮🐮\U0001fa75', 'ownerUsername': 'angelacedeno', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.2885-19/11380889_409398702576838_1266017959_a.jpg?stp=dst-jpg_e0_tt6&amp;_nc_cat=107&amp;cb=8438d1d6-89aba764&amp;ig_cache_key=GJmorQDGFD2QWHQBAKfmdUsAAAAAYUULAAAB1501500j-ccb7-5-cb8438d1d6-89aba764&amp;ccb=7-5&amp;_nc_sid=669407&amp;</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>6</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>anmodz</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>🥛🩵🫶🏻</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-06-01T16:45:39.000Z</t>
+        </is>
+      </c>
+      <c r="H30" s="1" t="n">
+        <v>46174.69836805556</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>16:45:39</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="b">
+        <v>0</v>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>https://instagram.com/anmodz</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/18085248638637794', 'id': '18085248638637794', 'text': '🥛\U0001fa75🫶🏻', 'ownerUsername': 'anmodz', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.82787-19/622460106_18558535039054809_8639843914683662196_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=107&amp;cb=8438d1d6-89aba764&amp;ig_cache_key=GMr8GSXZ842o4_5BAHQ-irlD5OZ3bmNDAQAB1501500j-ccb7-5-cb8438d1d6-89aba764&amp;ccb=7-5&amp;_</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>6</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>mariacongracia</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>🥛💙✨</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-06-01T15:50:11.000Z</t>
+        </is>
+      </c>
+      <c r="H31" s="1" t="n">
+        <v>46174.65984953703</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>15:50:11</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="b">
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>https://instagram.com/mariacongracia</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/17963981615936663', 'id': '17963981615936663', 'text': '🥛💙✨', 'ownerUsername': 'mariacongracia', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.75761-19/491449619_18500981782048355_2459432365914039453_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=110&amp;cb=8438d1d6-89aba764&amp;ig_cache_key=GBPtSh1jbh1-i7pBAJ2kZ8e0qCEibvEnAQAB1501500j-ccb7-5-cb8438d1d6-89aba764&amp;ccb=7-5&amp;_nc</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>dengoso92</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>🥹🥛🫶🏻 Gracias por tanto, perdón por tan poco</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-06-01T15:37:11.000Z</t>
+        </is>
+      </c>
+      <c r="H32" s="1" t="n">
+        <v>46174.65082175926</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>15:37:11</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="b">
+        <v>0</v>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>https://instagram.com/dengoso92</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/18133375870569037', 'id': '18133375870569037', 'text': '🥹🥛🫶🏻 Gracias por tanto, perdón por tan poco', 'ownerUsername': 'dengoso92', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.2885-19/473134923_3958307944414494_9203541198208029143_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=109&amp;cb=8438d1d6-89aba764&amp;ig_cache_key=GEt3MxwePfBiDxAOANfR3BL1i7l-bkULAAAB1501500j-ccb7-</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>6</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>arestrepo1</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>🥛 🩵 feliz día!</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-06-01T15:35:55.000Z</t>
+        </is>
+      </c>
+      <c r="H33" s="1" t="n">
+        <v>46174.64994212963</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>15:35:55</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>3</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="b">
+        <v>0</v>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>https://instagram.com/arestrepo1</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/18078646208649318', 'id': '18078646208649318', 'text': '🥛 \U0001fa75 feliz día!', 'ownerUsername': 'arestrepo1', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.2885-19/118281044_321495925960394_3774977018925045483_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=103&amp;cb=8438d1d6-89aba764&amp;ig_cache_key=GFTTDAfKrnYaZiQBAOtWShiZaWM0bkULAAAB1501500j-ccb7-5-cb8438d1d6-89aba76</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>6</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>valeriaaramirezs</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Sin leche no existirían unos manjaressss ✨✨ tqm alpina, feliz día de la leche💙</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-06-01T15:31:18.000Z</t>
+        </is>
+      </c>
+      <c r="H34" s="1" t="n">
+        <v>46174.64673611111</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>15:31:18</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>2</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>https://instagram.com/valeriaaramirezs</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/17971272774056843', 'id': '17971272774056843', 'text': 'Sin leche no existirían unos manjaressss ✨✨ tqm alpina, feliz día de la leche💙', 'ownerUsername': 'valeriaaramirezs', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.2885-19/482825497_1092176179342508_4902767707247043047_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=111&amp;cb=8438d1d6-89aba764&amp;ig_cache_key=GBlVxxys</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>7</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Naaaa necesito leche ya</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-06-16T01:04:43.000Z</t>
+        </is>
+      </c>
+      <c r="H35" s="1" t="n">
+        <v>46189.04494212963</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>46189</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>01:04:43</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="b">
+        <v>0</v>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1666265854630016', 'commentId': '1666265854630016', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE2NjYyNjU4NTQ2MzAwMTY=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNjY2MjY1ODU0NjMwMDE2', 'date': '2026-06-16T01:04:43.000Z', 'text': 'Naaaa necesito leche ya', 'author': {'__typename': 'User', 'id': 'pfbid0smM5DCinhycVUFyYFomSgXWW</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>7</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Es la verdad, sin LECHE no hay vida, el que entendió, entendió.</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-06-15T16:56:56.000Z</t>
+        </is>
+      </c>
+      <c r="H36" s="1" t="n">
+        <v>46188.7062037037</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>16:56:56</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="b">
+        <v>0</v>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=992117396794312', 'commentId': '992117396794312', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3Xzk5MjExNzM5Njc5NDMxMg==', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N185OTIxMTczOTY3OTQzMTI=', 'date': '2026-06-15T16:56:56.000Z', 'text': 'Es la verdad, sin LECHE no hay vida, el que entendió, entendió.', 'author': {'__typename': 'User',</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>7</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>sera que a Cepeda le apetecen los GAY.</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-06-14T18:01:29.000Z</t>
+        </is>
+      </c>
+      <c r="H37" s="1" t="n">
+        <v>46187.75103009259</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>18:01:29</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="b">
+        <v>0</v>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=2565559123889250', 'commentId': '2565559123889250', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzI1NjU1NTkxMjM4ODkyNTA=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18yNTY1NTU5MTIzODg5MjUw', 'date': '2026-06-14T18:01:29.000Z', 'text': 'sera que a Cepeda le apetecen los GAY.', 'author': {'__typename': 'User', 'id': 'pfbid02NDHz4Ltx</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>7</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Ese guerillo no se da lujos por qué es un burro con plata, plata si tiene y se hace pasar como pobre</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-06-14T00:55:09.000Z</t>
+        </is>
+      </c>
+      <c r="H38" s="1" t="n">
+        <v>46187.03829861111</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>00:55:09</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="b">
+        <v>0</v>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1002583355703915', 'commentId': '1002583355703915', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEwMDI1ODMzNTU3MDM5MTU=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMDAyNTgzMzU1NzAzOTE1', 'date': '2026-06-14T00:55:09.000Z', 'text': 'Ese guerillo no se da lujos por qué es un burro con plata, plata si tiene y se hace pasar como p</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>7</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Si gracias a guíen a Dios no me imagino un chicote sin leche .</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-06-14T00:50:20.000Z</t>
+        </is>
+      </c>
+      <c r="H39" s="1" t="n">
+        <v>46187.0349537037</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>00:50:20</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="b">
+        <v>0</v>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=992881343460117', 'commentId': '992881343460117', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3Xzk5Mjg4MTM0MzQ2MDExNw==', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N185OTI4ODEzNDM0NjAxMTc=', 'date': '2026-06-14T00:50:20.000Z', 'text': 'Si gracias a guíen a Dios no me imagino un chicote sin leche .', 'author': {'__typename': 'User', </t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>7</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Así mismo, con Los terroristas de Calarca,  Marquetalia y ELN.</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-06-13T01:08:36.000Z</t>
+        </is>
+      </c>
+      <c r="H40" s="1" t="n">
+        <v>46186.04763888889</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>01:08:36</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="b">
+        <v>0</v>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=2633929457004025', 'commentId': '2633929457004025', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzI2MzM5Mjk0NTcwMDQwMjU=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18yNjMzOTI5NDU3MDA0MDI1', 'date': '2026-06-13T01:08:36.000Z', 'text': 'Así mismo, con Los terroristas de Calarca,  Marquetalia y ELN.', 'author': {'__typename': 'User'</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>7</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Alpina cada ves es mas costoso y menor calidad en sus productos</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-06-12T15:00:39.000Z</t>
+        </is>
+      </c>
+      <c r="H41" s="1" t="n">
+        <v>46185.62545138889</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>15:00:39</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="b">
+        <v>0</v>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1307536754867709', 'commentId': '1307536754867709', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEzMDc1MzY3NTQ4Njc3MDk=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMzA3NTM2NzU0ODY3NzA5', 'date': '2026-06-12T15:00:39.000Z', 'text': 'Alpina cada ves es mas costoso y menor calidad en sus productos', 'author': {'__typename': 'User</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>7</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Q kk de portadas</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-06-12T05:43:49.000Z</t>
+        </is>
+      </c>
+      <c r="H42" s="1" t="n">
+        <v>46185.23876157407</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>05:43:49</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="b">
+        <v>0</v>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1035983095519441', 'commentId': '1035983095519441', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEwMzU5ODMwOTU1MTk0NDE=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMDM1OTgzMDk1NTE5NDQx', 'date': '2026-06-12T05:43:49.000Z', 'text': 'Q kk de portadas', 'author': {'__typename': 'User', 'id': 'pfbid0LB8Ru3XsT3hY1QV4ueQisAxaAFHHeCG</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>7</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-06-12T03:25:38.000Z</t>
+        </is>
+      </c>
+      <c r="H43" s="1" t="n">
+        <v>46185.14280092593</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>03:25:38</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="b">
+        <v>0</v>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1881514055848350', 'commentId': '1881514055848350', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE4ODE1MTQwNTU4NDgzNTA=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xODgxNTE0MDU1ODQ4MzUw', 'date': '2026-06-12T03:25:38.000Z', 'text': 'O', 'author': {'__typename': 'User', 'id': 'pfbid02KhiWnBqNqY8XRi58ujYM2wwEt2GUv7o75xUWYdTjA7cQv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>7</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>La leche es para el terneriro porque es un BEBE y necesita todos los nutrientes</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-06-12T00:41:51.000Z</t>
+        </is>
+      </c>
+      <c r="H44" s="1" t="n">
+        <v>46185.0290625</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>00:41:51</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="b">
+        <v>0</v>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1807637430664455', 'commentId': '1807637430664455', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE4MDc2Mzc0MzA2NjQ0NTU=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xODA3NjM3NDMwNjY0NDU1', 'date': '2026-06-12T00:41:51.000Z', 'text': 'La leche es para el terneriro porque es un BEBE y necesita todos los nutrientes', 'author': {'__</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>7</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Dios los maldiga por lo que le hacen a las vacas.</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-06-11T21:52:47.000Z</t>
+        </is>
+      </c>
+      <c r="H45" s="1" t="n">
+        <v>46184.91165509259</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>21:52:47</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="b">
+        <v>0</v>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=995084453485725', 'commentId': '995084453485725', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3Xzk5NTA4NDQ1MzQ4NTcyNQ==', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N185OTUwODQ0NTM0ODU3MjU=', 'date': '2026-06-11T21:52:47.000Z', 'text': 'Dios los maldiga por lo que le hacen a las vacas.', 'author': {'__typename': 'User', 'id': 'pfbid0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>7</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Me vi este video tomando justo leche alpina 😂</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-06-11T04:05:20.000Z</t>
+        </is>
+      </c>
+      <c r="H46" s="1" t="n">
+        <v>46184.17037037037</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>04:05:20</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="b">
+        <v>0</v>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=862717486357582', 'commentId': '862717486357582', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3Xzg2MjcxNzQ4NjM1NzU4Mg==', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N184NjI3MTc0ODYzNTc1ODI=', 'date': '2026-06-11T04:05:20.000Z', 'text': 'Me vi este video tomando justo leche alpina 😂', 'author': {'__typename': 'User', 'id': 'pfbid0Bkdc</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Cristhian Castro</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-06-11T03:46:14.000Z</t>
+        </is>
+      </c>
+      <c r="H47" s="1" t="n">
+        <v>46184.15710648148</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>03:46:14</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="b">
+        <v>0</v>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1650057302715364&amp;reply_comment_id=1670040630916580', 'commentId': '1650057302715364', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE2NzAwNDA2MzA5MTY1ODA=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNjcwMDQwNjMwOTE2NTgw', 'date': '2026-06-11T03:46:14.000Z', 'text': 'Cristhian Castro', 'author': {'__typename': 'User', '__isActor</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>7</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Sin leche no existirá alpina ni el vaso de yogurt agua a 4 mil pesos</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-06-11T02:35:14.000Z</t>
+        </is>
+      </c>
+      <c r="H48" s="1" t="n">
+        <v>46184.10780092593</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>02:35:14</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="b">
+        <v>0</v>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=870232606134016', 'commentId': '870232606134016', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3Xzg3MDIzMjYwNjEzNDAxNg==', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N184NzAyMzI2MDYxMzQwMTY=', 'date': '2026-06-11T02:35:14.000Z', 'text': 'Sin leche no existirá alpina ni el vaso de yogurt agua a 4 mil pesos', 'author': {'__typename': 'U</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>7</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Precio</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-06-10T17:34:25.000Z</t>
+        </is>
+      </c>
+      <c r="H49" s="1" t="n">
+        <v>46183.7322337963</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>46183</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>17:34:25</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="b">
+        <v>0</v>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1936632696995303', 'commentId': '1936632696995303', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE5MzY2MzI2OTY5OTUzMDM=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xOTM2NjMyNjk2OTk1MzAz', 'date': '2026-06-10T17:34:25.000Z', 'text': 'Precio', 'author': {'__typename': 'User', 'id': 'pfbid06JFUdP8sNBsNxGLkG7PJ9JsCZ6z1spVq4nzq8q46i</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>7</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Para eso la mejor leche es la de cabrá.  La leche de vaca es cancerígenas dice el pueblo . Como vivian los antecesores  ja</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-06-10T15:34:45.000Z</t>
+        </is>
+      </c>
+      <c r="H50" s="1" t="n">
+        <v>46183.64913194445</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>46183</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>15:34:45</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="b">
+        <v>0</v>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1763577697978693', 'commentId': '1763577697978693', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE3NjM1Nzc2OTc5Nzg2OTM=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNzYzNTc3Njk3OTc4Njkz', 'date': '2026-06-10T15:34:45.000Z', 'text': 'Para eso la mejor leche es la de cabrá.  La leche de vaca es cancerígenas dice el pueblo . Como </t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>7</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>y esa mala cara que es</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-06-09T21:17:04.000Z</t>
+        </is>
+      </c>
+      <c r="H51" s="1" t="n">
+        <v>46182.88685185185</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>46182</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>21:17:04</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="b">
+        <v>0</v>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1015387484765410', 'commentId': '1015387484765410', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEwMTUzODc0ODQ3NjU0MTA=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMDE1Mzg3NDg0NzY1NDEw', 'date': '2026-06-09T21:17:04.000Z', 'text': 'y esa mala cara que es', 'author': {'__typename': 'User', 'id': 'pfbid0yXRNeQ6URs5CBxdVUvs2x9XLQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>7</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Esa leche solo le cambia el color a la mierda</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-06-08T23:04:28.000Z</t>
+        </is>
+      </c>
+      <c r="H52" s="1" t="n">
+        <v>46181.96143518519</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>23:04:28</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="b">
+        <v>0</v>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=2205697686864259', 'commentId': '2205697686864259', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzIyMDU2OTc2ODY4NjQyNTk=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18yMjA1Njk3Njg2ODY0MjU5', 'date': '2026-06-08T23:04:28.000Z', 'text': 'Esa leche solo le cambia el color a la mierda', 'author': {'__typename': 'User', 'id': 'pfbid02r</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>7</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>ABELARDO DE LA SPRIELLA PRESIDENTE</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-06-08T21:05:06.000Z</t>
+        </is>
+      </c>
+      <c r="H53" s="1" t="n">
+        <v>46181.87854166667</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>21:05:06</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="b">
+        <v>0</v>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=943020682087299', 'commentId': '943020682087299', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3Xzk0MzAyMDY4MjA4NzI5OQ==', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N185NDMwMjA2ODIwODcyOTk=', 'date': '2026-06-08T21:05:06.000Z', 'text': 'ABELARDO DE LA SPRIELLA PRESIDENTE', 'author': {'__typename': 'User', 'id': 'pfbid02vjgMonnzExCrde</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>7</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Firmes</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-06-08T20:59:40.000Z</t>
+        </is>
+      </c>
+      <c r="H54" s="1" t="n">
+        <v>46181.87476851852</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>20:59:40</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="b">
+        <v>0</v>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1516416566587548', 'commentId': '1516416566587548', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE1MTY0MTY1NjY1ODc1NDg=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNTE2NDE2NTY2NTg3NTQ4', 'date': '2026-06-08T20:59:40.000Z', 'text': 'Firmes', 'author': {'__typename': 'User', 'id': 'pfbid033dc9dxdfw2m6VLbXXjTrk6YmJRRJEZK7hXJAJdxw</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>7</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Para mi la mejor leche es la de alpina</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-06-08T20:09:49.000Z</t>
+        </is>
+      </c>
+      <c r="H55" s="1" t="n">
+        <v>46181.84015046297</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>20:09:49</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="b">
+        <v>0</v>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=2602426543545930', 'commentId': '2602426543545930', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzI2MDI0MjY1NDM1NDU5MzA=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18yNjAyNDI2NTQzNTQ1OTMw', 'date': '2026-06-08T20:09:49.000Z', 'text': 'Para mi la mejor leche es la de alpina', 'author': {'__typename': 'User', 'id': 'pfbid03JpnjYcm7</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>7</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Bienvenido a mi vida</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-06-08T17:51:29.000Z</t>
+        </is>
+      </c>
+      <c r="H56" s="1" t="n">
+        <v>46181.74408564815</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>17:51:29</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="b">
+        <v>0</v>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1650057302715364', 'commentId': '1650057302715364', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE2NTAwNTczMDI3MTUzNjQ=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNjUwMDU3MzAyNzE1MzY0', 'date': '2026-06-08T17:51:29.000Z', 'text': 'Bienvenido a mi vida', 'author': {'__typename': 'User', 'id': '100003377225415', 'name': 'Cristh</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>7</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Leche esencial en la vida humana</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-06-08T17:44:38.000Z</t>
+        </is>
+      </c>
+      <c r="H57" s="1" t="n">
+        <v>46181.7393287037</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>17:44:38</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="b">
+        <v>0</v>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1656700515621731', 'commentId': '1656700515621731', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE2NTY3MDA1MTU2MjE3MzE=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNjU2NzAwNTE1NjIxNzMx', 'date': '2026-06-08T17:44:38.000Z', 'text': 'Leche esencial en la vida humana', 'author': {'__typename': 'User', 'id': 'pfbid02uS78LnA3epB5f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>7</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Me encanta gracias amigos</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-06-08T02:04:42.000Z</t>
+        </is>
+      </c>
+      <c r="H58" s="1" t="n">
+        <v>46181.08659722222</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>02:04:42</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="b">
+        <v>0</v>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=4483457891876445', 'commentId': '4483457891876445', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzQ0ODM0NTc4OTE4NzY0NDU=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N180NDgzNDU3ODkxODc2NDQ1', 'date': '2026-06-08T02:04:42.000Z', 'text': 'Me encanta gracias amigos', 'author': {'__typename': 'User', 'id': 'pfbid0tSSiFkv74fS5gkHE3SLXx7</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>7</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Si la leche de los hombres no salen preñadas las mujeres jajajajajajaa</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-06-07T12:58:30.000Z</t>
+        </is>
+      </c>
+      <c r="H59" s="1" t="n">
+        <v>46180.540625</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>46180</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>12:58:30</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="b">
+        <v>0</v>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=2460021841186072', 'commentId': '2460021841186072', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzI0NjAwMjE4NDExODYwNzI=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18yNDYwMDIxODQxMTg2MDcy', 'date': '2026-06-07T12:58:30.000Z', 'text': 'Si la leche de los hombres no salen preñadas las mujeres jajajajajajaa', 'author': {'__typename'</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>7</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Y de dónde sale la leche, de las vacas y de dónde salen la vacas del campo, y quien quiere meterle veneno a la tierra con el fracking si aguevardo firme por traicionar a la patria</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-06-06T18:14:51.000Z</t>
+        </is>
+      </c>
+      <c r="H60" s="1" t="n">
+        <v>46179.7603125</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>46179</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>18:14:51</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="b">
+        <v>0</v>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1536768038124120', 'commentId': '1536768038124120', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE1MzY3NjgwMzgxMjQxMjA=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNTM2NzY4MDM4MTI0MTIw', 'date': '2026-06-06T18:14:51.000Z', 'text': 'Y de dónde sale la leche, de las vacas y de dónde salen la vacas del campo, y quien quiere meter</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>7</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>PRESIDENTE PERO DE LA JUNTA DE ACCION COMUNAL DE MI BARRIO</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-06-06T03:04:25.000Z</t>
+        </is>
+      </c>
+      <c r="H61" s="1" t="n">
+        <v>46179.12806712963</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>46179</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>03:04:25</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="b">
+        <v>0</v>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1546422746896400', 'commentId': '1546422746896400', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE1NDY0MjI3NDY4OTY0MDA=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNTQ2NDIyNzQ2ODk2NDAw', 'date': '2026-06-06T03:04:25.000Z', 'text': 'PRESIDENTE PERO DE LA JUNTA DE ACCION COMUNAL DE MI BARRIO', 'author': {'__typename': 'User', 'i</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>7</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Que paso con la avena deslactosada?</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2026-06-06T01:38:41.000Z</t>
+        </is>
+      </c>
+      <c r="H62" s="1" t="n">
+        <v>46179.06853009259</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>46179</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>01:38:41</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="b">
+        <v>0</v>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1980454275946084', 'commentId': '1980454275946084', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE5ODA0NTQyNzU5NDYwODQ=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xOTgwNDU0Mjc1OTQ2MDg0', 'date': '2026-06-06T01:38:41.000Z', 'text': 'Que paso con la avena deslactosada?', 'author': {'__typename': 'User', 'id': 'pfbid03kGevmUFRf8G</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>7</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Dios hizo todo perfecto.</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2026-06-05T23:04:25.000Z</t>
+        </is>
+      </c>
+      <c r="H63" s="1" t="n">
+        <v>46178.96140046296</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>23:04:25</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="b">
+        <v>0</v>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=2220326995402183', 'commentId': '2220326995402183', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzIyMjAzMjY5OTU0MDIxODM=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18yMjIwMzI2OTk1NDAyMTgz', 'date': '2026-06-05T23:04:25.000Z', 'text': 'Dios hizo todo perfecto.', 'author': {'__typename': 'User', 'id': 'pfbid02uErgUfnAByUnNENfqqduqh</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>7</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Por eso le pagan a 1400 el litro de leche a los campesinos, porque les interesa el campo. Hipócritas avaros</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2026-06-05T22:56:31.000Z</t>
+        </is>
+      </c>
+      <c r="H64" s="1" t="n">
+        <v>46178.95591435185</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>22:56:31</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="b">
+        <v>0</v>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1466980861417379', 'commentId': '1466980861417379', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE0NjY5ODA4NjE0MTczNzk=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNDY2OTgwODYxNDE3Mzc5', 'date': '2026-06-05T22:56:31.000Z', 'text': 'Por eso le pagan a 1400 el litro de leche a los campesinos, porque les interesa el campo. Hipócr</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>7</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Seríamos más sanos.</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2026-06-05T21:32:08.000Z</t>
+        </is>
+      </c>
+      <c r="H65" s="1" t="n">
+        <v>46178.89731481481</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>21:32:08</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="b">
+        <v>0</v>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1321750493434078', 'commentId': '1321750493434078', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEzMjE3NTA0OTM0MzQwNzg=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMzIxNzUwNDkzNDM0MDc4', 'date': '2026-06-05T21:32:08.000Z', 'text': 'Seríamos más sanos.', 'author': {'__typename': 'User', 'id': 'pfbid0211v2PgCsriu7ZieBTqNBdTzxeMs</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>7</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Leche o lactosuero es escurridura con saborizantes</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2026-06-05T19:40:16.000Z</t>
+        </is>
+      </c>
+      <c r="H66" s="1" t="n">
+        <v>46178.81962962963</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>19:40:16</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="b">
+        <v>0</v>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1742474310293914', 'commentId': '1742474310293914', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE3NDI0NzQzMTAyOTM5MTQ=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNzQyNDc0MzEwMjkzOTE0', 'date': '2026-06-05T19:40:16.000Z', 'text': 'Leche o lactosuero es escurridura con saborizantes', 'author': {'__typename': 'User', 'id': 'pfb</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>7</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Policías en cada mesa de votación para que prohíba el uso de celular porque toman foto y luego van a cobrar eso es fraude prohibido el uso del celular en la mesa de votación</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2026-06-05T18:36:29.000Z</t>
+        </is>
+      </c>
+      <c r="H67" s="1" t="n">
+        <v>46178.77533564815</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>18:36:29</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="b">
+        <v>0</v>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=807045099006490', 'commentId': '807045099006490', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzgwNzA0NTA5OTAwNjQ5MA==', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N184MDcwNDUwOTkwMDY0OTA=', 'date': '2026-06-05T18:36:29.000Z', 'text': 'Policías en cada mesa de votación para que prohíba el uso de celular porque toman foto y luego van</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>7</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Una vida sin leche sería más saludable..</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2026-06-05T15:45:53.000Z</t>
+        </is>
+      </c>
+      <c r="H68" s="1" t="n">
+        <v>46178.65686342592</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>15:45:53</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="b">
+        <v>0</v>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1613621236403186', 'commentId': '1613621236403186', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE2MTM2MjEyMzY0MDMxODY=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNjEzNjIxMjM2NDAzMTg2', 'date': '2026-06-05T15:45:53.000Z', 'text': 'Una vida sin leche sería más saludable..', 'author': {'__typename': 'User', 'id': 'pfbid0221FUN5</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>7</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Trabajadora</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2026-06-05T13:06:49.000Z</t>
+        </is>
+      </c>
+      <c r="H69" s="1" t="n">
+        <v>46178.54640046296</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>13:06:49</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="b">
+        <v>0</v>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=999855859294373', 'commentId': '999855859294373', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3Xzk5OTg1NTg1OTI5NDM3Mw==', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N185OTk4NTU4NTkyOTQzNzM=', 'date': '2026-06-05T13:06:49.000Z', 'text': 'Trabajadora', 'author': {'__typename': 'User', 'id': 'pfbid02xhav5AyvXr1QckJZhRiRiWLGAWcNSdMDKjxHR</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>7</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Un delicioso chocolate con azucar y con leche...y almojabanita...que rico, ...un dulce abrazo Sabina</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2026-06-05T11:07:42.000Z</t>
+        </is>
+      </c>
+      <c r="H70" s="1" t="n">
+        <v>46178.46368055556</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>11:07:42</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="b">
+        <v>0</v>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=4495969137304720', 'commentId': '4495969137304720', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzQ0OTU5NjkxMzczMDQ3MjA=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N180NDk1OTY5MTM3MzA0NzIw', 'date': '2026-06-05T11:07:42.000Z', 'text': 'Un delicioso chocolate con azucar y con leche...y almojabanita...que rico, ...un dulce abrazo Sa</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>7</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Después que no me falte leche en las bolas</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2026-06-04T17:56:00.000Z</t>
+        </is>
+      </c>
+      <c r="H71" s="1" t="n">
+        <v>46177.74722222222</v>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>17:56:00</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="b">
+        <v>0</v>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=967627006156085', 'commentId': '967627006156085', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3Xzk2NzYyNzAwNjE1NjA4NQ==', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N185Njc2MjcwMDYxNTYwODU=', 'date': '2026-06-04T17:56:00.000Z', 'text': 'Después que no me falte leche en las bolas', 'author': {'__typename': 'User', 'id': 'pfbid0dTnbRjk</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>7</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Dulomoco, dulzaina, duque, Dumas, Dumoriez, ducal, durante, dureza, durmiente, dubitación, duna, duma.</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2026-06-04T15:13:40.000Z</t>
+        </is>
+      </c>
+      <c r="H72" s="1" t="n">
+        <v>46177.63449074074</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>15:13:40</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="b">
+        <v>0</v>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=4360313190905352', 'commentId': '4360313190905352', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzQzNjAzMTMxOTA5MDUzNTI=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N180MzYwMzEzMTkwOTA1MzUy', 'date': '2026-06-04T15:13:40.000Z', 'text': 'Dulomoco, dulzaina, duque, Dumas, Dumoriez, ducal, durante, dureza, durmiente, dubitación, duna,</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>7</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Cuanto le dieron por decir babosadas malparido comiendo mierda ,bien llevado que estara y se vende por un tamal</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2026-06-04T12:54:09.000Z</t>
+        </is>
+      </c>
+      <c r="H73" s="1" t="n">
+        <v>46177.53760416667</v>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>12:54:09</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="b">
+        <v>0</v>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1801806774117258', 'commentId': '1801806774117258', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE4MDE4MDY3NzQxMTcyNTg=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xODAxODA2Nzc0MTE3MjU4', 'date': '2026-06-04T12:54:09.000Z', 'text': 'Cuanto le dieron por decir babosadas malparido comiendo mierda ,bien llevado que estara y se ven</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>7</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Claudia Patricia Marcillo Patiño Mi razón si tiene argumentos señora, a diferencia de sus posturas sin fundamento... Le dicen no al Fracking y hablan de ambientalismo cuando van en carro y básicamente no brincan cuando hay otras acciones mucho más contaminantes las cuales según ustedes son una solución sostenible...</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2026-06-04T03:34:37.000Z</t>
+        </is>
+      </c>
+      <c r="H74" s="1" t="n">
+        <v>46177.14903935185</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>03:34:37</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="b">
+        <v>0</v>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1018920390530674&amp;reply_comment_id=1071203365579173', 'commentId': '1018920390530674', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEwNzEyMDMzNjU1NzkxNzM=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMDcxMjAzMzY1NTc5MTcz', 'date': '2026-06-04T03:34:37.000Z', 'text': 'Claudia Patricia Marcillo Patiño Mi razón si tiene argumentos </t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>7</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Se Imagina  que les quitan las Distribuidoras a  los distribuidores y  A los empleados les  Roban las liquidaciones  y las semanas de cotización a pensión</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2026-06-03T23:46:58.000Z</t>
+        </is>
+      </c>
+      <c r="H75" s="1" t="n">
+        <v>46176.99094907408</v>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>23:46:58</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="b">
+        <v>0</v>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1324424726460303', 'commentId': '1324424726460303', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEzMjQ0MjQ3MjY0NjAzMDM=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMzI0NDI0NzI2NDYwMzAz', 'date': '2026-06-03T23:46:58.000Z', 'text': 'Se Imagina  que les quitan las Distribuidoras a  los distribuidores y  A los empleados les  Roba</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>7</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Juan David Restrepo de razón tu postura política te falta decir q lo tienes grande ese es el nivel de conocimiento de Abelardo y sus seguidores👌a falta de conocimiento el insulto se convierte en la mejor arma los pobres de derecha🙄</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2026-06-03T21:56:39.000Z</t>
+        </is>
+      </c>
+      <c r="H76" s="1" t="n">
+        <v>46176.91434027778</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>21:56:39</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="b">
+        <v>0</v>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1018920390530674&amp;reply_comment_id=4555030531385501', 'commentId': '1018920390530674', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzQ1NTUwMzA1MzEzODU1MDE=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N180NTU1MDMwNTMxMzg1NTAx', 'date': '2026-06-03T21:56:39.000Z', 'text': 'Juan David Restrepo de razón tu postura política te falta deci</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>7</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>La leche es un veneno para el ser humano. El queso no Pero la leche sí</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2026-06-03T17:29:55.000Z</t>
+        </is>
+      </c>
+      <c r="H77" s="1" t="n">
+        <v>46176.72910879629</v>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>17:29:55</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="b">
+        <v>0</v>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=2434426847025249', 'commentId': '2434426847025249', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzI0MzQ0MjY4NDcwMjUyNDk=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18yNDM0NDI2ODQ3MDI1MjQ5', 'date': '2026-06-03T17:29:55.000Z', 'text': 'La leche es un veneno para el ser humano. El queso no Pero la leche sí', 'author': {'__typename'</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>7</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Pues vayase que falta no hace. Esta demorado en abandonar el Pais de la Belleza que ud ensucia. Chao geton</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2026-06-03T16:44:57.000Z</t>
+        </is>
+      </c>
+      <c r="H78" s="1" t="n">
+        <v>46176.69788194444</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>16:44:57</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="b">
+        <v>0</v>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1248903487119558', 'commentId': '1248903487119558', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEyNDg5MDM0ODcxMTk1NTg=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMjQ4OTAzNDg3MTE5NTU4', 'date': '2026-06-03T16:44:57.000Z', 'text': 'Pues vayase que falta no hace. Esta demorado en abandonar el Pais de la Belleza que ud ensucia. </t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>7</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Claudia Patricia Marcillo Patiño No se le ha quitado la Urticaria?? Fue tanto el ardor de jopo que todavía le anda rascando?</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2026-06-03T03:44:06.000Z</t>
+        </is>
+      </c>
+      <c r="H79" s="1" t="n">
+        <v>46176.155625</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>03:44:06</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="b">
+        <v>0</v>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1018920390530674&amp;reply_comment_id=977093231802746', 'commentId': '1018920390530674', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3Xzk3NzA5MzIzMTgwMjc0Ng==', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N185NzcwOTMyMzE4MDI3NDY=', 'date': '2026-06-03T03:44:06.000Z', 'text': 'Claudia Patricia Marcillo Patiño No se le ha quitado la Urticar</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>7</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Sin agua no hay vida y así votan por el que va hacer fracking 🙄</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2026-06-03T03:25:17.000Z</t>
+        </is>
+      </c>
+      <c r="H80" s="1" t="n">
+        <v>46176.14255787037</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>03:25:17</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="b">
+        <v>0</v>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1018920390530674', 'commentId': '1018920390530674', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEwMTg5MjAzOTA1MzA2NzQ=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMDE4OTIwMzkwNTMwNjc0', 'date': '2026-06-03T03:25:17.000Z', 'text': 'Sin agua no hay vida y así votan por el que va hacer fracking 🙄', 'author': {'__typename': 'User</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>7</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Sin leche hay lactosuero... Y con lactosuero hay mas campesinos estafados con tus precios Alpina</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2026-06-03T01:15:06.000Z</t>
+        </is>
+      </c>
+      <c r="H81" s="1" t="n">
+        <v>46176.05215277777</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>01:15:06</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="b">
+        <v>0</v>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1014454464368440', 'commentId': '1014454464368440', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEwMTQ0NTQ0NjQzNjg0NDA=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMDE0NDU0NDY0MzY4NDQw', 'date': '2026-06-03T01:15:06.000Z', 'text': 'Sin leche hay lactosuero... Y con lactosuero hay mas campesinos estafados con tus precios Alpina</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>7</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>No viviría inflamado, cero pedos.</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2026-06-03T01:14:10.000Z</t>
+        </is>
+      </c>
+      <c r="H82" s="1" t="n">
+        <v>46176.05150462963</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>01:14:10</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="b">
+        <v>0</v>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1007770421655962', 'commentId': '1007770421655962', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEwMDc3NzA0MjE2NTU5NjI=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMDA3NzcwNDIxNjU1OTYy', 'date': '2026-06-03T01:14:10.000Z', 'text': 'No viviría inflamado, cero pedos.', 'author': {'__typename': 'User', 'id': 'pfbid0efuAd5w8fZgz6m</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>7</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Oralia orania odilia osneli Olivia oliva Osmani olimpia olimpa Odalis</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:39:17.000Z</t>
+        </is>
+      </c>
+      <c r="H83" s="1" t="n">
+        <v>46175.7772800926</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>46175</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>18:39:17</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="b">
+        <v>0</v>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1532475761552597', 'commentId': '1532475761552597', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE1MzI0NzU3NjE1NTI1OTc=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNTMyNDc1NzYxNTUyNTk3', 'date': '2026-06-02T18:39:17.000Z', 'text': 'Oralia orania odilia osneli Olivia oliva Osmani olimpia olimpa Odalis', 'author': {'__typename':</t>
         </is>
       </c>
     </row>
@@ -1186,7 +5652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1359,6 +5825,60 @@
       </c>
       <c r="G6" s="1" t="n">
         <v>46221.10013888889</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>22</v>
+      </c>
+      <c r="E7" t="n">
+        <v>16</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>46174.64673611111</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>46185.58851851852</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>49</v>
+      </c>
+      <c r="E8" t="n">
+        <v>28</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>46175.7772800926</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>46189.04494212963</v>
       </c>
     </row>
   </sheetData>
@@ -1409,16 +5929,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="D2" t="n">
-        <v>0.11</v>
+        <v>0.5</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -1428,16 +5948,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1483,10 +6003,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -1495,7 +6015,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/Comentarios Campaña.xlsx
+++ b/Comentarios Campaña.xlsx
@@ -19,11 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -54,10 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -423,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P72"/>
+  <dimension ref="A1:Q72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,6 +501,11 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>extraction_status</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>created_time_raw</t>
         </is>
       </c>
@@ -545,7 +547,7 @@
       <c r="H2" s="1" t="n">
         <v>46185.58851851852</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="I2" s="1" t="n">
         <v>46185</v>
       </c>
       <c r="J2" t="inlineStr">
@@ -568,7 +570,8 @@
           <t>https://instagram.com/bolaochoradio_jlm</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/18028010735820663', 'id': '18028010735820663', 'text': '❤️❤️❤️👏👏👏', 'ownerUsername': 'bolaochoradio_jlm', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.82787-19/609426657_18278152333304341_7731619025179557966_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=106&amp;ig_cache_key=GOEcUyQVIvr44e9AAE7Aeh6KOkxrbmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3Rh</t>
         </is>
@@ -611,7 +614,7 @@
       <c r="H3" s="1" t="n">
         <v>46180.75890046296</v>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="I3" s="1" t="n">
         <v>46180</v>
       </c>
       <c r="J3" t="inlineStr">
@@ -634,7 +637,8 @@
           <t>https://instagram.com/anmeyrojasguerrero</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/18115431067869225', 'id': '18115431067869225', 'text': 'Como así que descontinuaron el alpin de vainilla ??', 'ownerUsername': 'anmeyrojasguerrero', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.82787-19/747452351_18188931100388565_1874264507433900028_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=107&amp;ig_cache_key=GL83jSzVLBWJvJ5AAPxXuKSjuQIabmNDAQAB1501500j-ccb7-5&amp;</t>
         </is>
@@ -677,7 +681,7 @@
       <c r="H4" s="1" t="n">
         <v>46176.23453703704</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="I4" s="1" t="n">
         <v>46176</v>
       </c>
       <c r="J4" t="inlineStr">
@@ -700,7 +704,8 @@
           <t>https://instagram.com/lauraveronica_er</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/17898759165309051', 'id': '17898759165309051', 'text': '@sinergiaanimalcolombia', 'ownerUsername': 'lauraveronica_er', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.2885-19/411363410_702264891880776_6971867694952727024_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=102&amp;cb=8438d1d6-89aba764&amp;ig_cache_key=GFLohBhINWvJtH4CAPDBreK6DMFgbkULAAAB1501500j-ccb7-5-cb8438d1d6-8</t>
         </is>
@@ -743,7 +748,7 @@
       <c r="H5" s="1" t="n">
         <v>46176.06981481481</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="I5" s="1" t="n">
         <v>46176</v>
       </c>
       <c r="J5" t="inlineStr">
@@ -766,7 +771,8 @@
           <t>https://instagram.com/joujou0107</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/18103828820045784', 'id': '18103828820045784', 'text': 'Porque volvió el ruido que enloquece en la tienda alpina de la 79 .. parece que el@techo no solucionó el problema .. lo amplifico', 'ownerUsername': 'joujou0107', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.2885-19/372932570_1962546517445924_7694878205033810064_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=1</t>
         </is>
@@ -809,7 +815,7 @@
       <c r="H6" s="1" t="n">
         <v>46175.87527777778</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="I6" s="1" t="n">
         <v>46175</v>
       </c>
       <c r="J6" t="inlineStr">
@@ -832,7 +838,8 @@
           <t>https://instagram.com/yosoy_j_e_r_</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/18122781676709889', 'id': '18122781676709889', 'text': 'Un año mas de explotación animal 🥰', 'ownerUsername': 'yosoy_j_e_r_', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.82787-19/619396999_18387138832147571_3896305389898522995_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=104&amp;ig_cache_key=GIc-6yRzpIZeAVNBAHNhV80bdRI2bmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;</t>
         </is>
@@ -875,7 +882,7 @@
       <c r="H7" s="1" t="n">
         <v>46175.78790509259</v>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="I7" s="1" t="n">
         <v>46175</v>
       </c>
       <c r="J7" t="inlineStr">
@@ -898,7 +905,8 @@
           <t>https://instagram.com/lauraveronica_er</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/18053058014750981', 'id': '18053058014750981', 'text': '@yosoy_j_e_r_', 'ownerUsername': 'lauraveronica_er', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.2885-19/411363410_702264891880776_6971867694952727024_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=102&amp;cb=8438d1d6-89aba764&amp;ig_cache_key=GFLohBhINWvJtH4CAPDBreK6DMFgbkULAAAB1501500j-ccb7-5-cb8438d1d6-89aba764&amp;cc</t>
         </is>
@@ -941,7 +949,7 @@
       <c r="H8" s="1" t="n">
         <v>46175.78769675926</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I8" s="1" t="n">
         <v>46175</v>
       </c>
       <c r="J8" t="inlineStr">
@@ -964,7 +972,8 @@
           <t>https://instagram.com/lauraveronica_er</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/18142689715518670', 'id': '18142689715518670', 'text': 'Una vida sin leche sería hermosa! Una vida sin maltrato animal!', 'ownerUsername': 'lauraveronica_er', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.2885-19/411363410_702264891880776_6971867694952727024_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=102&amp;ig_cache_key=GFLohBhINWvJtH4CAPDBreK6DMFgbkULAAAB1501500j-</t>
         </is>
@@ -1007,7 +1016,7 @@
       <c r="H9" s="1" t="n">
         <v>46175.53020833333</v>
       </c>
-      <c r="I9" s="2" t="n">
+      <c r="I9" s="1" t="n">
         <v>46175</v>
       </c>
       <c r="J9" t="inlineStr">
@@ -1030,7 +1039,8 @@
           <t>https://instagram.com/milefierro031</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/18099626549328332', 'id': '18099626549328332', 'text': 'Sin leche no hay vida🔥💙🐮', 'ownerUsername': 'milefierro031', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.75761-19/506018127_17846179632500400_2172907525543103403_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GE85KR6wzpd9AWc-AKsLxcXhtycebvEnAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2Z</t>
         </is>
@@ -1073,7 +1083,7 @@
       <c r="H10" s="1" t="n">
         <v>46175.061875</v>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="I10" s="1" t="n">
         <v>46175</v>
       </c>
       <c r="J10" t="inlineStr">
@@ -1096,7 +1106,8 @@
           <t>https://instagram.com/nmoralesr</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/18133633018562481', 'id': '18133633018562481', 'text': '🥛\U0001fa75', 'ownerUsername': 'nmoralesr', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.82787-19/729929448_18596148781024346_1134176551830756346_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GOjWgStahEhKGRFCAPobc5SQZ70PbmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6In</t>
         </is>
@@ -1139,7 +1150,7 @@
       <c r="H11" s="1" t="n">
         <v>46175.02952546296</v>
       </c>
-      <c r="I11" s="2" t="n">
+      <c r="I11" s="1" t="n">
         <v>46175</v>
       </c>
       <c r="J11" t="inlineStr">
@@ -1162,7 +1173,8 @@
           <t>https://instagram.com/luisamaya.remote</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/18071152436679388', 'id': '18071152436679388', 'text': '🐮muuuuuuuuy cool', 'ownerUsername': 'luisamaya.remote', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.2885-19/51573136_293663161262767_2574048044513230848_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;cb=8438d1d6-89aba764&amp;ig_cache_key=GJDxEgOvImnIFQsBAAAAAAAP27gjbkULAAAB1501500j-ccb7-5-cb8438d1d6-89aba764&amp;</t>
         </is>
@@ -1205,7 +1217,7 @@
       <c r="H12" s="1" t="n">
         <v>46174.988125</v>
       </c>
-      <c r="I12" s="2" t="n">
+      <c r="I12" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="J12" t="inlineStr">
@@ -1228,7 +1240,8 @@
           <t>https://instagram.com/kellys_loving</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/18141486358464579', 'id': '18141486358464579', 'text': 'Feliz día @alpina 😍', 'ownerUsername': 'kellys_loving', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.2885-19/458543973_1237439730504604_639025001783379578_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=104&amp;cb=8438d1d6-89aba764&amp;ig_cache_key=GGXTVBucU5HjcWUEAHpG5HnaRd4IbkULAAAB1501500j-ccb7-5-cb8438d1d6-89aba764</t>
         </is>
@@ -1271,7 +1284,7 @@
       <c r="H13" s="1" t="n">
         <v>46174.95530092593</v>
       </c>
-      <c r="I13" s="2" t="n">
+      <c r="I13" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="J13" t="inlineStr">
@@ -1294,7 +1307,8 @@
           <t>https://instagram.com/mariaclaudiapico</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/18090521612625817', 'id': '18090521612625817', 'text': '💙💙💙💙', 'ownerUsername': 'mariaclaudiapico', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.2885-19/476488792_640473678517415_5706999738040182288_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=100&amp;ig_cache_key=GFikZhynlBjmgUYCABDmIVcGVjNPbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb</t>
         </is>
@@ -1337,7 +1351,7 @@
       <c r="H14" s="1" t="n">
         <v>46174.87137731481</v>
       </c>
-      <c r="I14" s="2" t="n">
+      <c r="I14" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="J14" t="inlineStr">
@@ -1360,7 +1374,8 @@
           <t>https://instagram.com/mari.sdlv</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/17875000764610500', 'id': '17875000764610500', 'text': 'Sin leche no habría felicidad !! 🥛💙 Feliz día Alpina 🥹', 'ownerUsername': 'mari.sdlv', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.82787-19/523013216_18050972795530937_5521465705616428750_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=104&amp;cb=8438d1d6-89aba764&amp;ig_cache_key=GGCMLB_57lOdQyFAAM7OxCbOL6BMbmNDAQAB1</t>
         </is>
@@ -1403,7 +1418,7 @@
       <c r="H15" s="1" t="n">
         <v>46174.77515046296</v>
       </c>
-      <c r="I15" s="2" t="n">
+      <c r="I15" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="J15" t="inlineStr">
@@ -1426,7 +1441,8 @@
           <t>https://instagram.com/soysanticruz</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/18107498516473913', 'id': '18107498516473913', 'text': '🙌🙌', 'ownerUsername': 'soysanticruz', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.75761-19/504146061_18508816267036736_3085562163605248657_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=102&amp;cb=8438d1d6-89aba764&amp;ig_cache_key=GI2oDB5ASM_aq8FBAJGaE5ZwHtIqbvEnAQAB1501500j-ccb7-5-cb8438d1d6-89aba764&amp;ccb=7-5&amp;_nc_si</t>
         </is>
@@ -1469,7 +1485,7 @@
       <c r="H16" s="1" t="n">
         <v>46174.77163194444</v>
       </c>
-      <c r="I16" s="2" t="n">
+      <c r="I16" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="J16" t="inlineStr">
@@ -1492,7 +1508,8 @@
           <t>https://instagram.com/buentipo.global</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/18103723295043425', 'id': '18103723295043425', 'text': '🥛', 'ownerUsername': 'buentipo.global', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.75761-19/502965801_18326550277203333_6666050328820338889_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=109&amp;cb=8438d1d6-89aba764&amp;ig_cache_key=GCmm_h2FJTt-5htBAMlQNrB0kYJcbvEnAQAB1501500j-ccb7-5-cb8438d1d6-89aba764&amp;ccb=7-5&amp;_nc_</t>
         </is>
@@ -1535,7 +1552,7 @@
       <c r="H17" s="1" t="n">
         <v>46174.76834490741</v>
       </c>
-      <c r="I17" s="2" t="n">
+      <c r="I17" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="J17" t="inlineStr">
@@ -1558,7 +1575,8 @@
           <t>https://instagram.com/sebasforeroarango</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/18091418609613636', 'id': '18091418609613636', 'text': '🥛\U0001fa75🫰🏻', 'ownerUsername': 'sebasforeroarango', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.82787-19/683746054_18589577845048358_5347870612495357067_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=106&amp;cb=8438d1d6-89aba764&amp;ig_cache_key=GAYjwSgmhPpfHwtCAItUieL8czdKbmNDAQAB1501500j-ccb7-5-cb8438d1d6-89aba76</t>
         </is>
@@ -1601,7 +1619,7 @@
       <c r="H18" s="1" t="n">
         <v>46174.72817129629</v>
       </c>
-      <c r="I18" s="2" t="n">
+      <c r="I18" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="J18" t="inlineStr">
@@ -1624,7 +1642,8 @@
           <t>https://instagram.com/angelacedeno</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/18331810513264757', 'id': '18331810513264757', 'text': '🥛🐮🐄🐮🐮\U0001fa75', 'ownerUsername': 'angelacedeno', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.2885-19/11380889_409398702576838_1266017959_a.jpg?stp=dst-jpg_e0_tt6&amp;_nc_cat=107&amp;cb=8438d1d6-89aba764&amp;ig_cache_key=GJmorQDGFD2QWHQBAKfmdUsAAAAAYUULAAAB1501500j-ccb7-5-cb8438d1d6-89aba764&amp;ccb=7-5&amp;_nc_sid=669407&amp;</t>
         </is>
@@ -1667,7 +1686,7 @@
       <c r="H19" s="1" t="n">
         <v>46174.69836805556</v>
       </c>
-      <c r="I19" s="2" t="n">
+      <c r="I19" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="J19" t="inlineStr">
@@ -1690,7 +1709,8 @@
           <t>https://instagram.com/anmodz</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/18085248638637794', 'id': '18085248638637794', 'text': '🥛\U0001fa75🫶🏻', 'ownerUsername': 'anmodz', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.82787-19/622460106_18558535039054809_8639843914683662196_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=107&amp;cb=8438d1d6-89aba764&amp;ig_cache_key=GMr8GSXZ842o4_5BAHQ-irlD5OZ3bmNDAQAB1501500j-ccb7-5-cb8438d1d6-89aba764&amp;ccb=7-5&amp;_</t>
         </is>
@@ -1733,7 +1753,7 @@
       <c r="H20" s="1" t="n">
         <v>46174.65984953703</v>
       </c>
-      <c r="I20" s="2" t="n">
+      <c r="I20" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="J20" t="inlineStr">
@@ -1756,7 +1776,8 @@
           <t>https://instagram.com/mariacongracia</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/17963981615936663', 'id': '17963981615936663', 'text': '🥛💙✨', 'ownerUsername': 'mariacongracia', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.75761-19/491449619_18500981782048355_2459432365914039453_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=110&amp;cb=8438d1d6-89aba764&amp;ig_cache_key=GBPtSh1jbh1-i7pBAJ2kZ8e0qCEibvEnAQAB1501500j-ccb7-5-cb8438d1d6-89aba764&amp;ccb=7-5&amp;_nc</t>
         </is>
@@ -1799,7 +1820,7 @@
       <c r="H21" s="1" t="n">
         <v>46174.65082175926</v>
       </c>
-      <c r="I21" s="2" t="n">
+      <c r="I21" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="J21" t="inlineStr">
@@ -1822,7 +1843,8 @@
           <t>https://instagram.com/dengoso92</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/18133375870569037', 'id': '18133375870569037', 'text': '🥹🥛🫶🏻 Gracias por tanto, perdón por tan poco', 'ownerUsername': 'dengoso92', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.2885-19/473134923_3958307944414494_9203541198208029143_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=109&amp;cb=8438d1d6-89aba764&amp;ig_cache_key=GEt3MxwePfBiDxAOANfR3BL1i7l-bkULAAAB1501500j-ccb7-</t>
         </is>
@@ -1865,7 +1887,7 @@
       <c r="H22" s="1" t="n">
         <v>46174.64994212963</v>
       </c>
-      <c r="I22" s="2" t="n">
+      <c r="I22" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="J22" t="inlineStr">
@@ -1888,7 +1910,8 @@
           <t>https://instagram.com/arestrepo1</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
         <is>
           <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/18078646208649318', 'id': '18078646208649318', 'text': '🥛 \U0001fa75 feliz día!', 'ownerUsername': 'arestrepo1', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.2885-19/118281044_321495925960394_3774977018925045483_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=103&amp;cb=8438d1d6-89aba764&amp;ig_cache_key=GFTTDAfKrnYaZiQBAOtWShiZaWM0bkULAAAB1501500j-ccb7-5-cb8438d1d6-89aba76</t>
         </is>
@@ -1931,7 +1954,7 @@
       <c r="H23" s="1" t="n">
         <v>46174.64673611111</v>
       </c>
-      <c r="I23" s="2" t="n">
+      <c r="I23" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="J23" t="inlineStr">
@@ -1954,7 +1977,8 @@
           <t>https://instagram.com/valeriaaramirezs</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
         <is>
           <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/17971272774056843', 'id': '17971272774056843', 'text': 'Sin leche no existirían unos manjaressss ✨✨ tqm alpina, feliz día de la leche💙', 'ownerUsername': 'valeriaaramirezs', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.2885-19/482825497_1092176179342508_4902767707247043047_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=111&amp;cb=8438d1d6-89aba764&amp;ig_cache_key=GBlVxxys</t>
         </is>
@@ -1993,7 +2017,7 @@
       <c r="H24" s="1" t="n">
         <v>46189.04494212963</v>
       </c>
-      <c r="I24" s="2" t="n">
+      <c r="I24" s="1" t="n">
         <v>46189</v>
       </c>
       <c r="J24" t="inlineStr">
@@ -2001,10 +2025,8 @@
           <t>01:04:43</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K24" t="n">
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -2014,7 +2036,8 @@
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1666265854630016', 'commentId': '1666265854630016', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE2NjYyNjU4NTQ2MzAwMTY=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNjY2MjY1ODU0NjMwMDE2', 'date': '2026-06-16T01:04:43.000Z', 'text': 'Naaaa necesito leche ya', 'author': {'__typename': 'User', 'id': 'pfbid0smM5DCinhycVUFyYFomSgXWW</t>
         </is>
@@ -2053,7 +2076,7 @@
       <c r="H25" s="1" t="n">
         <v>46188.7062037037</v>
       </c>
-      <c r="I25" s="2" t="n">
+      <c r="I25" s="1" t="n">
         <v>46188</v>
       </c>
       <c r="J25" t="inlineStr">
@@ -2061,10 +2084,8 @@
           <t>16:56:56</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K25" t="n">
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -2074,7 +2095,8 @@
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=992117396794312', 'commentId': '992117396794312', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3Xzk5MjExNzM5Njc5NDMxMg==', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N185OTIxMTczOTY3OTQzMTI=', 'date': '2026-06-15T16:56:56.000Z', 'text': 'Es la verdad, sin LECHE no hay vida, el que entendió, entendió.', 'author': {'__typename': 'User',</t>
         </is>
@@ -2113,7 +2135,7 @@
       <c r="H26" s="1" t="n">
         <v>46187.75103009259</v>
       </c>
-      <c r="I26" s="2" t="n">
+      <c r="I26" s="1" t="n">
         <v>46187</v>
       </c>
       <c r="J26" t="inlineStr">
@@ -2121,10 +2143,8 @@
           <t>18:01:29</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K26" t="n">
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -2134,7 +2154,8 @@
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=2565559123889250', 'commentId': '2565559123889250', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzI1NjU1NTkxMjM4ODkyNTA=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18yNTY1NTU5MTIzODg5MjUw', 'date': '2026-06-14T18:01:29.000Z', 'text': 'sera que a Cepeda le apetecen los GAY.', 'author': {'__typename': 'User', 'id': 'pfbid02NDHz4Ltx</t>
         </is>
@@ -2173,7 +2194,7 @@
       <c r="H27" s="1" t="n">
         <v>46187.03829861111</v>
       </c>
-      <c r="I27" s="2" t="n">
+      <c r="I27" s="1" t="n">
         <v>46187</v>
       </c>
       <c r="J27" t="inlineStr">
@@ -2181,10 +2202,8 @@
           <t>00:55:09</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K27" t="n">
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -2194,7 +2213,8 @@
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1002583355703915', 'commentId': '1002583355703915', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEwMDI1ODMzNTU3MDM5MTU=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMDAyNTgzMzU1NzAzOTE1', 'date': '2026-06-14T00:55:09.000Z', 'text': 'Ese guerillo no se da lujos por qué es un burro con plata, plata si tiene y se hace pasar como p</t>
         </is>
@@ -2233,7 +2253,7 @@
       <c r="H28" s="1" t="n">
         <v>46187.0349537037</v>
       </c>
-      <c r="I28" s="2" t="n">
+      <c r="I28" s="1" t="n">
         <v>46187</v>
       </c>
       <c r="J28" t="inlineStr">
@@ -2241,10 +2261,8 @@
           <t>00:50:20</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K28" t="n">
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -2254,7 +2272,8 @@
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
         <is>
           <t xml:space="preserve">{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=992881343460117', 'commentId': '992881343460117', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3Xzk5Mjg4MTM0MzQ2MDExNw==', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N185OTI4ODEzNDM0NjAxMTc=', 'date': '2026-06-14T00:50:20.000Z', 'text': 'Si gracias a guíen a Dios no me imagino un chicote sin leche .', 'author': {'__typename': 'User', </t>
         </is>
@@ -2293,7 +2312,7 @@
       <c r="H29" s="1" t="n">
         <v>46186.04763888889</v>
       </c>
-      <c r="I29" s="2" t="n">
+      <c r="I29" s="1" t="n">
         <v>46186</v>
       </c>
       <c r="J29" t="inlineStr">
@@ -2301,10 +2320,8 @@
           <t>01:08:36</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K29" t="n">
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -2314,7 +2331,8 @@
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=2633929457004025', 'commentId': '2633929457004025', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzI2MzM5Mjk0NTcwMDQwMjU=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18yNjMzOTI5NDU3MDA0MDI1', 'date': '2026-06-13T01:08:36.000Z', 'text': 'Así mismo, con Los terroristas de Calarca,  Marquetalia y ELN.', 'author': {'__typename': 'User'</t>
         </is>
@@ -2353,7 +2371,7 @@
       <c r="H30" s="1" t="n">
         <v>46185.62545138889</v>
       </c>
-      <c r="I30" s="2" t="n">
+      <c r="I30" s="1" t="n">
         <v>46185</v>
       </c>
       <c r="J30" t="inlineStr">
@@ -2361,10 +2379,8 @@
           <t>15:00:39</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="K30" t="n">
+        <v>1</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -2374,7 +2390,8 @@
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1307536754867709', 'commentId': '1307536754867709', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEzMDc1MzY3NTQ4Njc3MDk=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMzA3NTM2NzU0ODY3NzA5', 'date': '2026-06-12T15:00:39.000Z', 'text': 'Alpina cada ves es mas costoso y menor calidad en sus productos', 'author': {'__typename': 'User</t>
         </is>
@@ -2413,7 +2430,7 @@
       <c r="H31" s="1" t="n">
         <v>46185.23876157407</v>
       </c>
-      <c r="I31" s="2" t="n">
+      <c r="I31" s="1" t="n">
         <v>46185</v>
       </c>
       <c r="J31" t="inlineStr">
@@ -2421,10 +2438,8 @@
           <t>05:43:49</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K31" t="n">
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -2434,7 +2449,8 @@
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1035983095519441', 'commentId': '1035983095519441', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEwMzU5ODMwOTU1MTk0NDE=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMDM1OTgzMDk1NTE5NDQx', 'date': '2026-06-12T05:43:49.000Z', 'text': 'Q kk de portadas', 'author': {'__typename': 'User', 'id': 'pfbid0LB8Ru3XsT3hY1QV4ueQisAxaAFHHeCG</t>
         </is>
@@ -2473,7 +2489,7 @@
       <c r="H32" s="1" t="n">
         <v>46185.14280092593</v>
       </c>
-      <c r="I32" s="2" t="n">
+      <c r="I32" s="1" t="n">
         <v>46185</v>
       </c>
       <c r="J32" t="inlineStr">
@@ -2481,10 +2497,8 @@
           <t>03:25:38</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K32" t="n">
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -2494,7 +2508,8 @@
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1881514055848350', 'commentId': '1881514055848350', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE4ODE1MTQwNTU4NDgzNTA=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xODgxNTE0MDU1ODQ4MzUw', 'date': '2026-06-12T03:25:38.000Z', 'text': 'O', 'author': {'__typename': 'User', 'id': 'pfbid02KhiWnBqNqY8XRi58ujYM2wwEt2GUv7o75xUWYdTjA7cQv</t>
         </is>
@@ -2533,7 +2548,7 @@
       <c r="H33" s="1" t="n">
         <v>46185.0290625</v>
       </c>
-      <c r="I33" s="2" t="n">
+      <c r="I33" s="1" t="n">
         <v>46185</v>
       </c>
       <c r="J33" t="inlineStr">
@@ -2541,10 +2556,8 @@
           <t>00:41:51</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="K33" t="n">
+        <v>1</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -2554,7 +2567,8 @@
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1807637430664455', 'commentId': '1807637430664455', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE4MDc2Mzc0MzA2NjQ0NTU=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xODA3NjM3NDMwNjY0NDU1', 'date': '2026-06-12T00:41:51.000Z', 'text': 'La leche es para el terneriro porque es un BEBE y necesita todos los nutrientes', 'author': {'__</t>
         </is>
@@ -2593,7 +2607,7 @@
       <c r="H34" s="1" t="n">
         <v>46184.91165509259</v>
       </c>
-      <c r="I34" s="2" t="n">
+      <c r="I34" s="1" t="n">
         <v>46184</v>
       </c>
       <c r="J34" t="inlineStr">
@@ -2601,10 +2615,8 @@
           <t>21:52:47</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K34" t="n">
+        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -2614,7 +2626,8 @@
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=995084453485725', 'commentId': '995084453485725', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3Xzk5NTA4NDQ1MzQ4NTcyNQ==', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N185OTUwODQ0NTM0ODU3MjU=', 'date': '2026-06-11T21:52:47.000Z', 'text': 'Dios los maldiga por lo que le hacen a las vacas.', 'author': {'__typename': 'User', 'id': 'pfbid0</t>
         </is>
@@ -2653,7 +2666,7 @@
       <c r="H35" s="1" t="n">
         <v>46184.17037037037</v>
       </c>
-      <c r="I35" s="2" t="n">
+      <c r="I35" s="1" t="n">
         <v>46184</v>
       </c>
       <c r="J35" t="inlineStr">
@@ -2661,10 +2674,8 @@
           <t>04:05:20</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K35" t="n">
+        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -2674,7 +2685,8 @@
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=862717486357582', 'commentId': '862717486357582', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3Xzg2MjcxNzQ4NjM1NzU4Mg==', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N184NjI3MTc0ODYzNTc1ODI=', 'date': '2026-06-11T04:05:20.000Z', 'text': 'Me vi este video tomando justo leche alpina 😂', 'author': {'__typename': 'User', 'id': 'pfbid0Bkdc</t>
         </is>
@@ -2713,7 +2725,7 @@
       <c r="H36" s="1" t="n">
         <v>46184.15710648148</v>
       </c>
-      <c r="I36" s="2" t="n">
+      <c r="I36" s="1" t="n">
         <v>46184</v>
       </c>
       <c r="J36" t="inlineStr">
@@ -2721,10 +2733,8 @@
           <t>03:46:14</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K36" t="n">
+        <v>0</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -2734,7 +2744,8 @@
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1650057302715364&amp;reply_comment_id=1670040630916580', 'commentId': '1650057302715364', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE2NzAwNDA2MzA5MTY1ODA=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNjcwMDQwNjMwOTE2NTgw', 'date': '2026-06-11T03:46:14.000Z', 'text': 'Cristhian Castro', 'author': {'__typename': 'User', '__isActor</t>
         </is>
@@ -2773,7 +2784,7 @@
       <c r="H37" s="1" t="n">
         <v>46184.10780092593</v>
       </c>
-      <c r="I37" s="2" t="n">
+      <c r="I37" s="1" t="n">
         <v>46184</v>
       </c>
       <c r="J37" t="inlineStr">
@@ -2781,10 +2792,8 @@
           <t>02:35:14</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K37" t="n">
+        <v>0</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -2794,7 +2803,8 @@
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=870232606134016', 'commentId': '870232606134016', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3Xzg3MDIzMjYwNjEzNDAxNg==', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N184NzAyMzI2MDYxMzQwMTY=', 'date': '2026-06-11T02:35:14.000Z', 'text': 'Sin leche no existirá alpina ni el vaso de yogurt agua a 4 mil pesos', 'author': {'__typename': 'U</t>
         </is>
@@ -2833,7 +2843,7 @@
       <c r="H38" s="1" t="n">
         <v>46183.7322337963</v>
       </c>
-      <c r="I38" s="2" t="n">
+      <c r="I38" s="1" t="n">
         <v>46183</v>
       </c>
       <c r="J38" t="inlineStr">
@@ -2841,10 +2851,8 @@
           <t>17:34:25</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K38" t="n">
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -2854,7 +2862,8 @@
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1936632696995303', 'commentId': '1936632696995303', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE5MzY2MzI2OTY5OTUzMDM=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xOTM2NjMyNjk2OTk1MzAz', 'date': '2026-06-10T17:34:25.000Z', 'text': 'Precio', 'author': {'__typename': 'User', 'id': 'pfbid06JFUdP8sNBsNxGLkG7PJ9JsCZ6z1spVq4nzq8q46i</t>
         </is>
@@ -2893,7 +2902,7 @@
       <c r="H39" s="1" t="n">
         <v>46183.64913194445</v>
       </c>
-      <c r="I39" s="2" t="n">
+      <c r="I39" s="1" t="n">
         <v>46183</v>
       </c>
       <c r="J39" t="inlineStr">
@@ -2901,10 +2910,8 @@
           <t>15:34:45</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K39" t="n">
+        <v>0</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -2914,7 +2921,8 @@
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr">
         <is>
           <t xml:space="preserve">{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1763577697978693', 'commentId': '1763577697978693', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE3NjM1Nzc2OTc5Nzg2OTM=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNzYzNTc3Njk3OTc4Njkz', 'date': '2026-06-10T15:34:45.000Z', 'text': 'Para eso la mejor leche es la de cabrá.  La leche de vaca es cancerígenas dice el pueblo . Como </t>
         </is>
@@ -2953,7 +2961,7 @@
       <c r="H40" s="1" t="n">
         <v>46182.88685185185</v>
       </c>
-      <c r="I40" s="2" t="n">
+      <c r="I40" s="1" t="n">
         <v>46182</v>
       </c>
       <c r="J40" t="inlineStr">
@@ -2961,10 +2969,8 @@
           <t>21:17:04</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K40" t="n">
+        <v>0</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -2974,7 +2980,8 @@
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1015387484765410', 'commentId': '1015387484765410', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEwMTUzODc0ODQ3NjU0MTA=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMDE1Mzg3NDg0NzY1NDEw', 'date': '2026-06-09T21:17:04.000Z', 'text': 'y esa mala cara que es', 'author': {'__typename': 'User', 'id': 'pfbid0yXRNeQ6URs5CBxdVUvs2x9XLQ</t>
         </is>
@@ -3013,7 +3020,7 @@
       <c r="H41" s="1" t="n">
         <v>46181.96143518519</v>
       </c>
-      <c r="I41" s="2" t="n">
+      <c r="I41" s="1" t="n">
         <v>46181</v>
       </c>
       <c r="J41" t="inlineStr">
@@ -3021,10 +3028,8 @@
           <t>23:04:28</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K41" t="n">
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -3034,7 +3039,8 @@
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=2205697686864259', 'commentId': '2205697686864259', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzIyMDU2OTc2ODY4NjQyNTk=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18yMjA1Njk3Njg2ODY0MjU5', 'date': '2026-06-08T23:04:28.000Z', 'text': 'Esa leche solo le cambia el color a la mierda', 'author': {'__typename': 'User', 'id': 'pfbid02r</t>
         </is>
@@ -3073,7 +3079,7 @@
       <c r="H42" s="1" t="n">
         <v>46181.87854166667</v>
       </c>
-      <c r="I42" s="2" t="n">
+      <c r="I42" s="1" t="n">
         <v>46181</v>
       </c>
       <c r="J42" t="inlineStr">
@@ -3081,10 +3087,8 @@
           <t>21:05:06</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K42" t="n">
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -3094,7 +3098,8 @@
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=943020682087299', 'commentId': '943020682087299', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3Xzk0MzAyMDY4MjA4NzI5OQ==', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N185NDMwMjA2ODIwODcyOTk=', 'date': '2026-06-08T21:05:06.000Z', 'text': 'ABELARDO DE LA SPRIELLA PRESIDENTE', 'author': {'__typename': 'User', 'id': 'pfbid02vjgMonnzExCrde</t>
         </is>
@@ -3133,7 +3138,7 @@
       <c r="H43" s="1" t="n">
         <v>46181.87476851852</v>
       </c>
-      <c r="I43" s="2" t="n">
+      <c r="I43" s="1" t="n">
         <v>46181</v>
       </c>
       <c r="J43" t="inlineStr">
@@ -3141,10 +3146,8 @@
           <t>20:59:40</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K43" t="n">
+        <v>0</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -3154,7 +3157,8 @@
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1516416566587548', 'commentId': '1516416566587548', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE1MTY0MTY1NjY1ODc1NDg=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNTE2NDE2NTY2NTg3NTQ4', 'date': '2026-06-08T20:59:40.000Z', 'text': 'Firmes', 'author': {'__typename': 'User', 'id': 'pfbid033dc9dxdfw2m6VLbXXjTrk6YmJRRJEZK7hXJAJdxw</t>
         </is>
@@ -3193,7 +3197,7 @@
       <c r="H44" s="1" t="n">
         <v>46181.84015046297</v>
       </c>
-      <c r="I44" s="2" t="n">
+      <c r="I44" s="1" t="n">
         <v>46181</v>
       </c>
       <c r="J44" t="inlineStr">
@@ -3201,10 +3205,8 @@
           <t>20:09:49</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K44" t="n">
+        <v>0</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -3214,7 +3216,8 @@
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=2602426543545930', 'commentId': '2602426543545930', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzI2MDI0MjY1NDM1NDU5MzA=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18yNjAyNDI2NTQzNTQ1OTMw', 'date': '2026-06-08T20:09:49.000Z', 'text': 'Para mi la mejor leche es la de alpina', 'author': {'__typename': 'User', 'id': 'pfbid03JpnjYcm7</t>
         </is>
@@ -3253,7 +3256,7 @@
       <c r="H45" s="1" t="n">
         <v>46181.74408564815</v>
       </c>
-      <c r="I45" s="2" t="n">
+      <c r="I45" s="1" t="n">
         <v>46181</v>
       </c>
       <c r="J45" t="inlineStr">
@@ -3261,10 +3264,8 @@
           <t>17:51:29</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="K45" t="n">
+        <v>1</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -3274,7 +3275,8 @@
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1650057302715364', 'commentId': '1650057302715364', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE2NTAwNTczMDI3MTUzNjQ=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNjUwMDU3MzAyNzE1MzY0', 'date': '2026-06-08T17:51:29.000Z', 'text': 'Bienvenido a mi vida', 'author': {'__typename': 'User', 'id': '100003377225415', 'name': 'Cristh</t>
         </is>
@@ -3313,7 +3315,7 @@
       <c r="H46" s="1" t="n">
         <v>46181.7393287037</v>
       </c>
-      <c r="I46" s="2" t="n">
+      <c r="I46" s="1" t="n">
         <v>46181</v>
       </c>
       <c r="J46" t="inlineStr">
@@ -3321,10 +3323,8 @@
           <t>17:44:38</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K46" t="n">
+        <v>0</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -3334,7 +3334,8 @@
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1656700515621731', 'commentId': '1656700515621731', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE2NTY3MDA1MTU2MjE3MzE=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNjU2NzAwNTE1NjIxNzMx', 'date': '2026-06-08T17:44:38.000Z', 'text': 'Leche esencial en la vida humana', 'author': {'__typename': 'User', 'id': 'pfbid02uS78LnA3epB5f8</t>
         </is>
@@ -3373,7 +3374,7 @@
       <c r="H47" s="1" t="n">
         <v>46181.08659722222</v>
       </c>
-      <c r="I47" s="2" t="n">
+      <c r="I47" s="1" t="n">
         <v>46181</v>
       </c>
       <c r="J47" t="inlineStr">
@@ -3381,10 +3382,8 @@
           <t>02:04:42</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K47" t="n">
+        <v>0</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -3394,7 +3393,8 @@
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=4483457891876445', 'commentId': '4483457891876445', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzQ0ODM0NTc4OTE4NzY0NDU=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N180NDgzNDU3ODkxODc2NDQ1', 'date': '2026-06-08T02:04:42.000Z', 'text': 'Me encanta gracias amigos', 'author': {'__typename': 'User', 'id': 'pfbid0tSSiFkv74fS5gkHE3SLXx7</t>
         </is>
@@ -3433,7 +3433,7 @@
       <c r="H48" s="1" t="n">
         <v>46180.540625</v>
       </c>
-      <c r="I48" s="2" t="n">
+      <c r="I48" s="1" t="n">
         <v>46180</v>
       </c>
       <c r="J48" t="inlineStr">
@@ -3441,10 +3441,8 @@
           <t>12:58:30</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K48" t="n">
+        <v>0</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -3454,7 +3452,8 @@
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=2460021841186072', 'commentId': '2460021841186072', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzI0NjAwMjE4NDExODYwNzI=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18yNDYwMDIxODQxMTg2MDcy', 'date': '2026-06-07T12:58:30.000Z', 'text': 'Si la leche de los hombres no salen preñadas las mujeres jajajajajajaa', 'author': {'__typename'</t>
         </is>
@@ -3493,7 +3492,7 @@
       <c r="H49" s="1" t="n">
         <v>46179.7603125</v>
       </c>
-      <c r="I49" s="2" t="n">
+      <c r="I49" s="1" t="n">
         <v>46179</v>
       </c>
       <c r="J49" t="inlineStr">
@@ -3501,10 +3500,8 @@
           <t>18:14:51</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K49" t="n">
+        <v>0</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -3514,7 +3511,8 @@
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr">
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1536768038124120', 'commentId': '1536768038124120', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE1MzY3NjgwMzgxMjQxMjA=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNTM2NzY4MDM4MTI0MTIw', 'date': '2026-06-06T18:14:51.000Z', 'text': 'Y de dónde sale la leche, de las vacas y de dónde salen la vacas del campo, y quien quiere meter</t>
         </is>
@@ -3553,7 +3551,7 @@
       <c r="H50" s="1" t="n">
         <v>46179.12806712963</v>
       </c>
-      <c r="I50" s="2" t="n">
+      <c r="I50" s="1" t="n">
         <v>46179</v>
       </c>
       <c r="J50" t="inlineStr">
@@ -3561,10 +3559,8 @@
           <t>03:04:25</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K50" t="n">
+        <v>0</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -3574,7 +3570,8 @@
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1546422746896400', 'commentId': '1546422746896400', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE1NDY0MjI3NDY4OTY0MDA=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNTQ2NDIyNzQ2ODk2NDAw', 'date': '2026-06-06T03:04:25.000Z', 'text': 'PRESIDENTE PERO DE LA JUNTA DE ACCION COMUNAL DE MI BARRIO', 'author': {'__typename': 'User', 'i</t>
         </is>
@@ -3613,7 +3610,7 @@
       <c r="H51" s="1" t="n">
         <v>46179.06853009259</v>
       </c>
-      <c r="I51" s="2" t="n">
+      <c r="I51" s="1" t="n">
         <v>46179</v>
       </c>
       <c r="J51" t="inlineStr">
@@ -3621,10 +3618,8 @@
           <t>01:38:41</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K51" t="n">
+        <v>0</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -3634,7 +3629,8 @@
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1980454275946084', 'commentId': '1980454275946084', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE5ODA0NTQyNzU5NDYwODQ=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xOTgwNDU0Mjc1OTQ2MDg0', 'date': '2026-06-06T01:38:41.000Z', 'text': 'Que paso con la avena deslactosada?', 'author': {'__typename': 'User', 'id': 'pfbid03kGevmUFRf8G</t>
         </is>
@@ -3673,7 +3669,7 @@
       <c r="H52" s="1" t="n">
         <v>46178.96140046296</v>
       </c>
-      <c r="I52" s="2" t="n">
+      <c r="I52" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="J52" t="inlineStr">
@@ -3681,10 +3677,8 @@
           <t>23:04:25</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="K52" t="n">
+        <v>3</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -3694,7 +3688,8 @@
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr">
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=2220326995402183', 'commentId': '2220326995402183', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzIyMjAzMjY5OTU0MDIxODM=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18yMjIwMzI2OTk1NDAyMTgz', 'date': '2026-06-05T23:04:25.000Z', 'text': 'Dios hizo todo perfecto.', 'author': {'__typename': 'User', 'id': 'pfbid02uErgUfnAByUnNENfqqduqh</t>
         </is>
@@ -3733,7 +3728,7 @@
       <c r="H53" s="1" t="n">
         <v>46178.95591435185</v>
       </c>
-      <c r="I53" s="2" t="n">
+      <c r="I53" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="J53" t="inlineStr">
@@ -3741,10 +3736,8 @@
           <t>22:56:31</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K53" t="n">
+        <v>0</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -3754,7 +3747,8 @@
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr">
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1466980861417379', 'commentId': '1466980861417379', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE0NjY5ODA4NjE0MTczNzk=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNDY2OTgwODYxNDE3Mzc5', 'date': '2026-06-05T22:56:31.000Z', 'text': 'Por eso le pagan a 1400 el litro de leche a los campesinos, porque les interesa el campo. Hipócr</t>
         </is>
@@ -3793,7 +3787,7 @@
       <c r="H54" s="1" t="n">
         <v>46178.89731481481</v>
       </c>
-      <c r="I54" s="2" t="n">
+      <c r="I54" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="J54" t="inlineStr">
@@ -3801,10 +3795,8 @@
           <t>21:32:08</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="K54" t="n">
+        <v>3</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -3814,7 +3806,8 @@
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1321750493434078', 'commentId': '1321750493434078', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEzMjE3NTA0OTM0MzQwNzg=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMzIxNzUwNDkzNDM0MDc4', 'date': '2026-06-05T21:32:08.000Z', 'text': 'Seríamos más sanos.', 'author': {'__typename': 'User', 'id': 'pfbid0211v2PgCsriu7ZieBTqNBdTzxeMs</t>
         </is>
@@ -3853,7 +3846,7 @@
       <c r="H55" s="1" t="n">
         <v>46178.81962962963</v>
       </c>
-      <c r="I55" s="2" t="n">
+      <c r="I55" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="J55" t="inlineStr">
@@ -3861,10 +3854,8 @@
           <t>19:40:16</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="K55" t="n">
+        <v>10</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -3874,7 +3865,8 @@
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1742474310293914', 'commentId': '1742474310293914', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE3NDI0NzQzMTAyOTM5MTQ=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNzQyNDc0MzEwMjkzOTE0', 'date': '2026-06-05T19:40:16.000Z', 'text': 'Leche o lactosuero es escurridura con saborizantes', 'author': {'__typename': 'User', 'id': 'pfb</t>
         </is>
@@ -3913,7 +3905,7 @@
       <c r="H56" s="1" t="n">
         <v>46178.77533564815</v>
       </c>
-      <c r="I56" s="2" t="n">
+      <c r="I56" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="J56" t="inlineStr">
@@ -3921,10 +3913,8 @@
           <t>18:36:29</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K56" t="n">
+        <v>0</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -3934,7 +3924,8 @@
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=807045099006490', 'commentId': '807045099006490', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzgwNzA0NTA5OTAwNjQ5MA==', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N184MDcwNDUwOTkwMDY0OTA=', 'date': '2026-06-05T18:36:29.000Z', 'text': 'Policías en cada mesa de votación para que prohíba el uso de celular porque toman foto y luego van</t>
         </is>
@@ -3973,7 +3964,7 @@
       <c r="H57" s="1" t="n">
         <v>46178.65686342592</v>
       </c>
-      <c r="I57" s="2" t="n">
+      <c r="I57" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="J57" t="inlineStr">
@@ -3981,10 +3972,8 @@
           <t>15:45:53</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K57" t="n">
+        <v>0</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -3994,7 +3983,8 @@
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr">
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1613621236403186', 'commentId': '1613621236403186', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE2MTM2MjEyMzY0MDMxODY=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNjEzNjIxMjM2NDAzMTg2', 'date': '2026-06-05T15:45:53.000Z', 'text': 'Una vida sin leche sería más saludable..', 'author': {'__typename': 'User', 'id': 'pfbid0221FUN5</t>
         </is>
@@ -4033,7 +4023,7 @@
       <c r="H58" s="1" t="n">
         <v>46178.54640046296</v>
       </c>
-      <c r="I58" s="2" t="n">
+      <c r="I58" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="J58" t="inlineStr">
@@ -4041,10 +4031,8 @@
           <t>13:06:49</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="K58" t="n">
+        <v>3</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -4054,7 +4042,8 @@
       </c>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=999855859294373', 'commentId': '999855859294373', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3Xzk5OTg1NTg1OTI5NDM3Mw==', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N185OTk4NTU4NTkyOTQzNzM=', 'date': '2026-06-05T13:06:49.000Z', 'text': 'Trabajadora', 'author': {'__typename': 'User', 'id': 'pfbid02xhav5AyvXr1QckJZhRiRiWLGAWcNSdMDKjxHR</t>
         </is>
@@ -4093,7 +4082,7 @@
       <c r="H59" s="1" t="n">
         <v>46178.46368055556</v>
       </c>
-      <c r="I59" s="2" t="n">
+      <c r="I59" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="J59" t="inlineStr">
@@ -4101,10 +4090,8 @@
           <t>11:07:42</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="K59" t="n">
+        <v>4</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -4114,7 +4101,8 @@
       </c>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=4495969137304720', 'commentId': '4495969137304720', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzQ0OTU5NjkxMzczMDQ3MjA=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N180NDk1OTY5MTM3MzA0NzIw', 'date': '2026-06-05T11:07:42.000Z', 'text': 'Un delicioso chocolate con azucar y con leche...y almojabanita...que rico, ...un dulce abrazo Sa</t>
         </is>
@@ -4153,7 +4141,7 @@
       <c r="H60" s="1" t="n">
         <v>46177.74722222222</v>
       </c>
-      <c r="I60" s="2" t="n">
+      <c r="I60" s="1" t="n">
         <v>46177</v>
       </c>
       <c r="J60" t="inlineStr">
@@ -4161,10 +4149,8 @@
           <t>17:56:00</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K60" t="n">
+        <v>0</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -4174,7 +4160,8 @@
       </c>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr">
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=967627006156085', 'commentId': '967627006156085', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3Xzk2NzYyNzAwNjE1NjA4NQ==', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N185Njc2MjcwMDYxNTYwODU=', 'date': '2026-06-04T17:56:00.000Z', 'text': 'Después que no me falte leche en las bolas', 'author': {'__typename': 'User', 'id': 'pfbid0dTnbRjk</t>
         </is>
@@ -4213,7 +4200,7 @@
       <c r="H61" s="1" t="n">
         <v>46177.63449074074</v>
       </c>
-      <c r="I61" s="2" t="n">
+      <c r="I61" s="1" t="n">
         <v>46177</v>
       </c>
       <c r="J61" t="inlineStr">
@@ -4221,10 +4208,8 @@
           <t>15:13:40</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K61" t="n">
+        <v>0</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -4234,7 +4219,8 @@
       </c>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr">
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=4360313190905352', 'commentId': '4360313190905352', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzQzNjAzMTMxOTA5MDUzNTI=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N180MzYwMzEzMTkwOTA1MzUy', 'date': '2026-06-04T15:13:40.000Z', 'text': 'Dulomoco, dulzaina, duque, Dumas, Dumoriez, ducal, durante, dureza, durmiente, dubitación, duna,</t>
         </is>
@@ -4273,7 +4259,7 @@
       <c r="H62" s="1" t="n">
         <v>46177.53760416667</v>
       </c>
-      <c r="I62" s="2" t="n">
+      <c r="I62" s="1" t="n">
         <v>46177</v>
       </c>
       <c r="J62" t="inlineStr">
@@ -4281,10 +4267,8 @@
           <t>12:54:09</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K62" t="n">
+        <v>0</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -4294,7 +4278,8 @@
       </c>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr">
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1801806774117258', 'commentId': '1801806774117258', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE4MDE4MDY3NzQxMTcyNTg=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xODAxODA2Nzc0MTE3MjU4', 'date': '2026-06-04T12:54:09.000Z', 'text': 'Cuanto le dieron por decir babosadas malparido comiendo mierda ,bien llevado que estara y se ven</t>
         </is>
@@ -4333,7 +4318,7 @@
       <c r="H63" s="1" t="n">
         <v>46177.14903935185</v>
       </c>
-      <c r="I63" s="2" t="n">
+      <c r="I63" s="1" t="n">
         <v>46177</v>
       </c>
       <c r="J63" t="inlineStr">
@@ -4341,10 +4326,8 @@
           <t>03:34:37</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K63" t="n">
+        <v>0</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -4354,7 +4337,8 @@
       </c>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr">
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr">
         <is>
           <t xml:space="preserve">{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1018920390530674&amp;reply_comment_id=1071203365579173', 'commentId': '1018920390530674', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEwNzEyMDMzNjU1NzkxNzM=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMDcxMjAzMzY1NTc5MTcz', 'date': '2026-06-04T03:34:37.000Z', 'text': 'Claudia Patricia Marcillo Patiño Mi razón si tiene argumentos </t>
         </is>
@@ -4393,7 +4377,7 @@
       <c r="H64" s="1" t="n">
         <v>46176.99094907408</v>
       </c>
-      <c r="I64" s="2" t="n">
+      <c r="I64" s="1" t="n">
         <v>46176</v>
       </c>
       <c r="J64" t="inlineStr">
@@ -4401,10 +4385,8 @@
           <t>23:46:58</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K64" t="n">
+        <v>0</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -4414,7 +4396,8 @@
       </c>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr">
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1324424726460303', 'commentId': '1324424726460303', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEzMjQ0MjQ3MjY0NjAzMDM=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMzI0NDI0NzI2NDYwMzAz', 'date': '2026-06-03T23:46:58.000Z', 'text': 'Se Imagina  que les quitan las Distribuidoras a  los distribuidores y  A los empleados les  Roba</t>
         </is>
@@ -4453,7 +4436,7 @@
       <c r="H65" s="1" t="n">
         <v>46176.91434027778</v>
       </c>
-      <c r="I65" s="2" t="n">
+      <c r="I65" s="1" t="n">
         <v>46176</v>
       </c>
       <c r="J65" t="inlineStr">
@@ -4461,10 +4444,8 @@
           <t>21:56:39</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K65" t="n">
+        <v>0</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -4474,7 +4455,8 @@
       </c>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr">
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1018920390530674&amp;reply_comment_id=4555030531385501', 'commentId': '1018920390530674', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzQ1NTUwMzA1MzEzODU1MDE=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N180NTU1MDMwNTMxMzg1NTAx', 'date': '2026-06-03T21:56:39.000Z', 'text': 'Juan David Restrepo de razón tu postura política te falta deci</t>
         </is>
@@ -4513,7 +4495,7 @@
       <c r="H66" s="1" t="n">
         <v>46176.72910879629</v>
       </c>
-      <c r="I66" s="2" t="n">
+      <c r="I66" s="1" t="n">
         <v>46176</v>
       </c>
       <c r="J66" t="inlineStr">
@@ -4521,10 +4503,8 @@
           <t>17:29:55</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K66" t="n">
+        <v>0</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -4534,7 +4514,8 @@
       </c>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr">
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=2434426847025249', 'commentId': '2434426847025249', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzI0MzQ0MjY4NDcwMjUyNDk=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18yNDM0NDI2ODQ3MDI1MjQ5', 'date': '2026-06-03T17:29:55.000Z', 'text': 'La leche es un veneno para el ser humano. El queso no Pero la leche sí', 'author': {'__typename'</t>
         </is>
@@ -4573,7 +4554,7 @@
       <c r="H67" s="1" t="n">
         <v>46176.69788194444</v>
       </c>
-      <c r="I67" s="2" t="n">
+      <c r="I67" s="1" t="n">
         <v>46176</v>
       </c>
       <c r="J67" t="inlineStr">
@@ -4581,10 +4562,8 @@
           <t>16:44:57</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K67" t="n">
+        <v>0</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -4594,7 +4573,8 @@
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr">
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr">
         <is>
           <t xml:space="preserve">{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1248903487119558', 'commentId': '1248903487119558', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEyNDg5MDM0ODcxMTk1NTg=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMjQ4OTAzNDg3MTE5NTU4', 'date': '2026-06-03T16:44:57.000Z', 'text': 'Pues vayase que falta no hace. Esta demorado en abandonar el Pais de la Belleza que ud ensucia. </t>
         </is>
@@ -4633,7 +4613,7 @@
       <c r="H68" s="1" t="n">
         <v>46176.155625</v>
       </c>
-      <c r="I68" s="2" t="n">
+      <c r="I68" s="1" t="n">
         <v>46176</v>
       </c>
       <c r="J68" t="inlineStr">
@@ -4641,10 +4621,8 @@
           <t>03:44:06</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="K68" t="n">
+        <v>1</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -4654,7 +4632,8 @@
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr">
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1018920390530674&amp;reply_comment_id=977093231802746', 'commentId': '1018920390530674', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3Xzk3NzA5MzIzMTgwMjc0Ng==', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N185NzcwOTMyMzE4MDI3NDY=', 'date': '2026-06-03T03:44:06.000Z', 'text': 'Claudia Patricia Marcillo Patiño No se le ha quitado la Urticar</t>
         </is>
@@ -4693,7 +4672,7 @@
       <c r="H69" s="1" t="n">
         <v>46176.14255787037</v>
       </c>
-      <c r="I69" s="2" t="n">
+      <c r="I69" s="1" t="n">
         <v>46176</v>
       </c>
       <c r="J69" t="inlineStr">
@@ -4701,10 +4680,8 @@
           <t>03:25:17</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K69" t="n">
+        <v>0</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -4714,7 +4691,8 @@
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr">
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1018920390530674', 'commentId': '1018920390530674', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEwMTg5MjAzOTA1MzA2NzQ=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMDE4OTIwMzkwNTMwNjc0', 'date': '2026-06-03T03:25:17.000Z', 'text': 'Sin agua no hay vida y así votan por el que va hacer fracking 🙄', 'author': {'__typename': 'User</t>
         </is>
@@ -4753,7 +4731,7 @@
       <c r="H70" s="1" t="n">
         <v>46176.05215277777</v>
       </c>
-      <c r="I70" s="2" t="n">
+      <c r="I70" s="1" t="n">
         <v>46176</v>
       </c>
       <c r="J70" t="inlineStr">
@@ -4761,10 +4739,8 @@
           <t>01:15:06</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K70" t="n">
+        <v>0</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -4774,7 +4750,8 @@
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr">
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1014454464368440', 'commentId': '1014454464368440', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEwMTQ0NTQ0NjQzNjg0NDA=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMDE0NDU0NDY0MzY4NDQw', 'date': '2026-06-03T01:15:06.000Z', 'text': 'Sin leche hay lactosuero... Y con lactosuero hay mas campesinos estafados con tus precios Alpina</t>
         </is>
@@ -4813,7 +4790,7 @@
       <c r="H71" s="1" t="n">
         <v>46176.05150462963</v>
       </c>
-      <c r="I71" s="2" t="n">
+      <c r="I71" s="1" t="n">
         <v>46176</v>
       </c>
       <c r="J71" t="inlineStr">
@@ -4821,10 +4798,8 @@
           <t>01:14:10</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="K71" t="n">
+        <v>1</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
@@ -4834,7 +4809,8 @@
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr">
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1007770421655962', 'commentId': '1007770421655962', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEwMDc3NzA0MjE2NTU5NjI=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMDA3NzcwNDIxNjU1OTYy', 'date': '2026-06-03T01:14:10.000Z', 'text': 'No viviría inflamado, cero pedos.', 'author': {'__typename': 'User', 'id': 'pfbid0efuAd5w8fZgz6m</t>
         </is>
@@ -4873,7 +4849,7 @@
       <c r="H72" s="1" t="n">
         <v>46175.7772800926</v>
       </c>
-      <c r="I72" s="2" t="n">
+      <c r="I72" s="1" t="n">
         <v>46175</v>
       </c>
       <c r="J72" t="inlineStr">
@@ -4881,10 +4857,8 @@
           <t>18:39:17</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K72" t="n">
+        <v>0</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
@@ -4894,7 +4868,8 @@
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr">
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1532475761552597', 'commentId': '1532475761552597', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE1MzI0NzU3NjE1NTI1OTc=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNTMyNDc1NzYxNTUyNTk3', 'date': '2026-06-02T18:39:17.000Z', 'text': 'Oralia orania odilia osneli Olivia oliva Osmani olimpia olimpa Odalis', 'author': {'__typename':</t>
         </is>

--- a/Comentarios Campaña.xlsx
+++ b/Comentarios Campaña.xlsx
@@ -5114,7 +5114,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/Comentarios Campaña.xlsx
+++ b/Comentarios Campaña.xlsx
@@ -5114,7 +5114,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Comentarios Campaña.xlsx
+++ b/Comentarios Campaña.xlsx
@@ -19,9 +19,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -52,9 +54,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q72"/>
+  <dimension ref="A1:Q73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1871,32 +1874,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>arestrepo1</t>
+          <t>islannder</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>🥛 🩵 feliz día!</t>
+          <t>🥛💙👏</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-06-01T15:35:55.000Z</t>
+          <t>2026-06-01T15:36:22.000Z</t>
         </is>
       </c>
       <c r="H22" s="1" t="n">
-        <v>46174.64994212963</v>
-      </c>
-      <c r="I22" s="1" t="n">
+        <v>46174.65025462963</v>
+      </c>
+      <c r="I22" s="2" t="n">
         <v>46174</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>15:35:55</t>
+          <t>15:36:22</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -1907,13 +1910,13 @@
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>https://instagram.com/arestrepo1</t>
+          <t>https://instagram.com/islannder</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/18078646208649318', 'id': '18078646208649318', 'text': '🥛 \U0001fa75 feliz día!', 'ownerUsername': 'arestrepo1', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.2885-19/118281044_321495925960394_3774977018925045483_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=103&amp;cb=8438d1d6-89aba764&amp;ig_cache_key=GFTTDAfKrnYaZiQBAOtWShiZaWM0bkULAAAB1501500j-ccb7-5-cb8438d1d6-89aba76</t>
+          <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/18211792327335801', 'id': '18211792327335801', 'text': '🥛💙👏', 'ownerUsername': 'islannder', 'ownerProfilePicUrl': 'https://scontent-lax7-1.cdninstagram.com/v/t51.2885-19/448126487_365367639905992_2995606017369638556_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=105&amp;ig_cache_key=GBfetRrIlmPITEwBAJwGVyjNh5IpbkULAAAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfc</t>
         </is>
       </c>
     </row>
@@ -1938,32 +1941,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>valeriaaramirezs</t>
+          <t>arestrepo1</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sin leche no existirían unos manjaressss ✨✨ tqm alpina, feliz día de la leche💙</t>
+          <t>🥛 🩵 feliz día!</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-06-01T15:31:18.000Z</t>
+          <t>2026-06-01T15:35:55.000Z</t>
         </is>
       </c>
       <c r="H23" s="1" t="n">
-        <v>46174.64673611111</v>
+        <v>46174.64994212963</v>
       </c>
       <c r="I23" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>15:31:18</t>
+          <t>15:35:55</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -1974,59 +1977,63 @@
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
-          <t>https://instagram.com/valeriaaramirezs</t>
+          <t>https://instagram.com/arestrepo1</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/17971272774056843', 'id': '17971272774056843', 'text': 'Sin leche no existirían unos manjaressss ✨✨ tqm alpina, feliz día de la leche💙', 'ownerUsername': 'valeriaaramirezs', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.2885-19/482825497_1092176179342508_4902767707247043047_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=111&amp;cb=8438d1d6-89aba764&amp;ig_cache_key=GBlVxxys</t>
+          <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/18078646208649318', 'id': '18078646208649318', 'text': '🥛 \U0001fa75 feliz día!', 'ownerUsername': 'arestrepo1', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.2885-19/118281044_321495925960394_3774977018925045483_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=103&amp;cb=8438d1d6-89aba764&amp;ig_cache_key=GFTTDAfKrnYaZiQBAOtWShiZaWM0bkULAAAB1501500j-ccb7-5-cb8438d1d6-89aba76</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
+          <t>https://www.instagram.com/p/DZDrlIMgOkl/</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>valeriaaramirezs</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Naaaa necesito leche ya</t>
+          <t>Sin leche no existirían unos manjaressss ✨✨ tqm alpina, feliz día de la leche💙</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-06-16T01:04:43.000Z</t>
+          <t>2026-06-01T15:31:18.000Z</t>
         </is>
       </c>
       <c r="H24" s="1" t="n">
-        <v>46189.04494212963</v>
+        <v>46174.64673611111</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>46189</v>
+        <v>46174</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>01:04:43</t>
+          <t>15:31:18</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -2035,11 +2042,15 @@
         <v>0</v>
       </c>
       <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>https://instagram.com/valeriaaramirezs</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1666265854630016', 'commentId': '1666265854630016', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE2NjYyNjU4NTQ2MzAwMTY=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNjY2MjY1ODU0NjMwMDE2', 'date': '2026-06-16T01:04:43.000Z', 'text': 'Naaaa necesito leche ya', 'author': {'__typename': 'User', 'id': 'pfbid0smM5DCinhycVUFyYFomSgXWW</t>
+          <t>{'postUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/', 'commentUrl': 'https://www.instagram.com/p/DZDrlIMgOkl/c/17971272774056843', 'id': '17971272774056843', 'text': 'Sin leche no existirían unos manjaressss ✨✨ tqm alpina, feliz día de la leche💙', 'ownerUsername': 'valeriaaramirezs', 'ownerProfilePicUrl': 'https://scontent-cph2-1.cdninstagram.com/v/t51.2885-19/482825497_1092176179342508_4902767707247043047_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=111&amp;cb=8438d1d6-89aba764&amp;ig_cache_key=GBlVxxys</t>
         </is>
       </c>
     </row>
@@ -2065,23 +2076,23 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Es la verdad, sin LECHE no hay vida, el que entendió, entendió.</t>
+          <t>Naaaa necesito leche ya</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-06-15T16:56:56.000Z</t>
+          <t>2026-06-16T01:04:43.000Z</t>
         </is>
       </c>
       <c r="H25" s="1" t="n">
-        <v>46188.7062037037</v>
+        <v>46189.04494212963</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>16:56:56</t>
+          <t>01:04:43</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -2098,7 +2109,7 @@
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=992117396794312', 'commentId': '992117396794312', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3Xzk5MjExNzM5Njc5NDMxMg==', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N185OTIxMTczOTY3OTQzMTI=', 'date': '2026-06-15T16:56:56.000Z', 'text': 'Es la verdad, sin LECHE no hay vida, el que entendió, entendió.', 'author': {'__typename': 'User',</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1666265854630016', 'commentId': '1666265854630016', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE2NjYyNjU4NTQ2MzAwMTY=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNjY2MjY1ODU0NjMwMDE2', 'date': '2026-06-16T01:04:43.000Z', 'text': 'Naaaa necesito leche ya', 'author': {'__typename': 'User', 'id': 'pfbid0smM5DCinhycVUFyYFomSgXWW</t>
         </is>
       </c>
     </row>
@@ -2124,23 +2135,23 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>sera que a Cepeda le apetecen los GAY.</t>
+          <t>Es la verdad, sin LECHE no hay vida, el que entendió, entendió.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-06-14T18:01:29.000Z</t>
+          <t>2026-06-15T16:56:56.000Z</t>
         </is>
       </c>
       <c r="H26" s="1" t="n">
-        <v>46187.75103009259</v>
+        <v>46188.7062037037</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>18:01:29</t>
+          <t>16:56:56</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -2157,7 +2168,7 @@
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=2565559123889250', 'commentId': '2565559123889250', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzI1NjU1NTkxMjM4ODkyNTA=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18yNTY1NTU5MTIzODg5MjUw', 'date': '2026-06-14T18:01:29.000Z', 'text': 'sera que a Cepeda le apetecen los GAY.', 'author': {'__typename': 'User', 'id': 'pfbid02NDHz4Ltx</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=992117396794312', 'commentId': '992117396794312', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3Xzk5MjExNzM5Njc5NDMxMg==', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N185OTIxMTczOTY3OTQzMTI=', 'date': '2026-06-15T16:56:56.000Z', 'text': 'Es la verdad, sin LECHE no hay vida, el que entendió, entendió.', 'author': {'__typename': 'User',</t>
         </is>
       </c>
     </row>
@@ -2183,23 +2194,23 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ese guerillo no se da lujos por qué es un burro con plata, plata si tiene y se hace pasar como pobre</t>
+          <t>sera que a Cepeda le apetecen los GAY.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-06-14T00:55:09.000Z</t>
+          <t>2026-06-14T18:01:29.000Z</t>
         </is>
       </c>
       <c r="H27" s="1" t="n">
-        <v>46187.03829861111</v>
+        <v>46187.75103009259</v>
       </c>
       <c r="I27" s="1" t="n">
         <v>46187</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>00:55:09</t>
+          <t>18:01:29</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2216,7 +2227,7 @@
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1002583355703915', 'commentId': '1002583355703915', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEwMDI1ODMzNTU3MDM5MTU=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMDAyNTgzMzU1NzAzOTE1', 'date': '2026-06-14T00:55:09.000Z', 'text': 'Ese guerillo no se da lujos por qué es un burro con plata, plata si tiene y se hace pasar como p</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=2565559123889250', 'commentId': '2565559123889250', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzI1NjU1NTkxMjM4ODkyNTA=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18yNTY1NTU5MTIzODg5MjUw', 'date': '2026-06-14T18:01:29.000Z', 'text': 'sera que a Cepeda le apetecen los GAY.', 'author': {'__typename': 'User', 'id': 'pfbid02NDHz4Ltx</t>
         </is>
       </c>
     </row>
@@ -2242,23 +2253,23 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Si gracias a guíen a Dios no me imagino un chicote sin leche .</t>
+          <t>Ese guerillo no se da lujos por qué es un burro con plata, plata si tiene y se hace pasar como pobre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-06-14T00:50:20.000Z</t>
+          <t>2026-06-14T00:55:09.000Z</t>
         </is>
       </c>
       <c r="H28" s="1" t="n">
-        <v>46187.0349537037</v>
+        <v>46187.03829861111</v>
       </c>
       <c r="I28" s="1" t="n">
         <v>46187</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>00:50:20</t>
+          <t>00:55:09</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2275,7 +2286,7 @@
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
-          <t xml:space="preserve">{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=992881343460117', 'commentId': '992881343460117', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3Xzk5Mjg4MTM0MzQ2MDExNw==', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N185OTI4ODEzNDM0NjAxMTc=', 'date': '2026-06-14T00:50:20.000Z', 'text': 'Si gracias a guíen a Dios no me imagino un chicote sin leche .', 'author': {'__typename': 'User', </t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1002583355703915', 'commentId': '1002583355703915', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEwMDI1ODMzNTU3MDM5MTU=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMDAyNTgzMzU1NzAzOTE1', 'date': '2026-06-14T00:55:09.000Z', 'text': 'Ese guerillo no se da lujos por qué es un burro con plata, plata si tiene y se hace pasar como p</t>
         </is>
       </c>
     </row>
@@ -2301,23 +2312,23 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Así mismo, con Los terroristas de Calarca,  Marquetalia y ELN.</t>
+          <t>Si gracias a guíen a Dios no me imagino un chicote sin leche .</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-06-13T01:08:36.000Z</t>
+          <t>2026-06-14T00:50:20.000Z</t>
         </is>
       </c>
       <c r="H29" s="1" t="n">
-        <v>46186.04763888889</v>
+        <v>46187.0349537037</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>01:08:36</t>
+          <t>00:50:20</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2334,7 +2345,7 @@
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=2633929457004025', 'commentId': '2633929457004025', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzI2MzM5Mjk0NTcwMDQwMjU=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18yNjMzOTI5NDU3MDA0MDI1', 'date': '2026-06-13T01:08:36.000Z', 'text': 'Así mismo, con Los terroristas de Calarca,  Marquetalia y ELN.', 'author': {'__typename': 'User'</t>
+          <t xml:space="preserve">{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=992881343460117', 'commentId': '992881343460117', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3Xzk5Mjg4MTM0MzQ2MDExNw==', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N185OTI4ODEzNDM0NjAxMTc=', 'date': '2026-06-14T00:50:20.000Z', 'text': 'Si gracias a guíen a Dios no me imagino un chicote sin leche .', 'author': {'__typename': 'User', </t>
         </is>
       </c>
     </row>
@@ -2360,27 +2371,27 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Alpina cada ves es mas costoso y menor calidad en sus productos</t>
+          <t>Así mismo, con Los terroristas de Calarca,  Marquetalia y ELN.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-06-12T15:00:39.000Z</t>
+          <t>2026-06-13T01:08:36.000Z</t>
         </is>
       </c>
       <c r="H30" s="1" t="n">
-        <v>46185.62545138889</v>
+        <v>46186.04763888889</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>15:00:39</t>
+          <t>01:08:36</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -2393,7 +2404,7 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1307536754867709', 'commentId': '1307536754867709', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEzMDc1MzY3NTQ4Njc3MDk=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMzA3NTM2NzU0ODY3NzA5', 'date': '2026-06-12T15:00:39.000Z', 'text': 'Alpina cada ves es mas costoso y menor calidad en sus productos', 'author': {'__typename': 'User</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=2633929457004025', 'commentId': '2633929457004025', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzI2MzM5Mjk0NTcwMDQwMjU=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18yNjMzOTI5NDU3MDA0MDI1', 'date': '2026-06-13T01:08:36.000Z', 'text': 'Así mismo, con Los terroristas de Calarca,  Marquetalia y ELN.', 'author': {'__typename': 'User'</t>
         </is>
       </c>
     </row>
@@ -2419,27 +2430,27 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Q kk de portadas</t>
+          <t>Alpina cada ves es mas costoso y menor calidad en sus productos</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-06-12T05:43:49.000Z</t>
+          <t>2026-06-12T15:00:39.000Z</t>
         </is>
       </c>
       <c r="H31" s="1" t="n">
-        <v>46185.23876157407</v>
+        <v>46185.62545138889</v>
       </c>
       <c r="I31" s="1" t="n">
         <v>46185</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>05:43:49</t>
+          <t>15:00:39</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -2452,7 +2463,7 @@
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1035983095519441', 'commentId': '1035983095519441', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEwMzU5ODMwOTU1MTk0NDE=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMDM1OTgzMDk1NTE5NDQx', 'date': '2026-06-12T05:43:49.000Z', 'text': 'Q kk de portadas', 'author': {'__typename': 'User', 'id': 'pfbid0LB8Ru3XsT3hY1QV4ueQisAxaAFHHeCG</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1307536754867709', 'commentId': '1307536754867709', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEzMDc1MzY3NTQ4Njc3MDk=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMzA3NTM2NzU0ODY3NzA5', 'date': '2026-06-12T15:00:39.000Z', 'text': 'Alpina cada ves es mas costoso y menor calidad en sus productos', 'author': {'__typename': 'User</t>
         </is>
       </c>
     </row>
@@ -2478,23 +2489,23 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>Q kk de portadas</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-06-12T03:25:38.000Z</t>
+          <t>2026-06-12T05:43:49.000Z</t>
         </is>
       </c>
       <c r="H32" s="1" t="n">
-        <v>46185.14280092593</v>
+        <v>46185.23876157407</v>
       </c>
       <c r="I32" s="1" t="n">
         <v>46185</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>03:25:38</t>
+          <t>05:43:49</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2511,7 +2522,7 @@
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1881514055848350', 'commentId': '1881514055848350', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE4ODE1MTQwNTU4NDgzNTA=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xODgxNTE0MDU1ODQ4MzUw', 'date': '2026-06-12T03:25:38.000Z', 'text': 'O', 'author': {'__typename': 'User', 'id': 'pfbid02KhiWnBqNqY8XRi58ujYM2wwEt2GUv7o75xUWYdTjA7cQv</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1035983095519441', 'commentId': '1035983095519441', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEwMzU5ODMwOTU1MTk0NDE=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMDM1OTgzMDk1NTE5NDQx', 'date': '2026-06-12T05:43:49.000Z', 'text': 'Q kk de portadas', 'author': {'__typename': 'User', 'id': 'pfbid0LB8Ru3XsT3hY1QV4ueQisAxaAFHHeCG</t>
         </is>
       </c>
     </row>
@@ -2537,27 +2548,27 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>La leche es para el terneriro porque es un BEBE y necesita todos los nutrientes</t>
+          <t>O</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-06-12T00:41:51.000Z</t>
+          <t>2026-06-12T03:25:38.000Z</t>
         </is>
       </c>
       <c r="H33" s="1" t="n">
-        <v>46185.0290625</v>
+        <v>46185.14280092593</v>
       </c>
       <c r="I33" s="1" t="n">
         <v>46185</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>00:41:51</t>
+          <t>03:25:38</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -2570,7 +2581,7 @@
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1807637430664455', 'commentId': '1807637430664455', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE4MDc2Mzc0MzA2NjQ0NTU=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xODA3NjM3NDMwNjY0NDU1', 'date': '2026-06-12T00:41:51.000Z', 'text': 'La leche es para el terneriro porque es un BEBE y necesita todos los nutrientes', 'author': {'__</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1881514055848350', 'commentId': '1881514055848350', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE4ODE1MTQwNTU4NDgzNTA=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xODgxNTE0MDU1ODQ4MzUw', 'date': '2026-06-12T03:25:38.000Z', 'text': 'O', 'author': {'__typename': 'User', 'id': 'pfbid02KhiWnBqNqY8XRi58ujYM2wwEt2GUv7o75xUWYdTjA7cQv</t>
         </is>
       </c>
     </row>
@@ -2596,27 +2607,27 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dios los maldiga por lo que le hacen a las vacas.</t>
+          <t>La leche es para el terneriro porque es un BEBE y necesita todos los nutrientes</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-06-11T21:52:47.000Z</t>
+          <t>2026-06-12T00:41:51.000Z</t>
         </is>
       </c>
       <c r="H34" s="1" t="n">
-        <v>46184.91165509259</v>
+        <v>46185.0290625</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>21:52:47</t>
+          <t>00:41:51</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -2629,7 +2640,7 @@
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=995084453485725', 'commentId': '995084453485725', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3Xzk5NTA4NDQ1MzQ4NTcyNQ==', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N185OTUwODQ0NTM0ODU3MjU=', 'date': '2026-06-11T21:52:47.000Z', 'text': 'Dios los maldiga por lo que le hacen a las vacas.', 'author': {'__typename': 'User', 'id': 'pfbid0</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1807637430664455', 'commentId': '1807637430664455', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE4MDc2Mzc0MzA2NjQ0NTU=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xODA3NjM3NDMwNjY0NDU1', 'date': '2026-06-12T00:41:51.000Z', 'text': 'La leche es para el terneriro porque es un BEBE y necesita todos los nutrientes', 'author': {'__</t>
         </is>
       </c>
     </row>
@@ -2655,23 +2666,23 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Me vi este video tomando justo leche alpina 😂</t>
+          <t>Dios los maldiga por lo que le hacen a las vacas.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-06-11T04:05:20.000Z</t>
+          <t>2026-06-11T21:52:47.000Z</t>
         </is>
       </c>
       <c r="H35" s="1" t="n">
-        <v>46184.17037037037</v>
+        <v>46184.91165509259</v>
       </c>
       <c r="I35" s="1" t="n">
         <v>46184</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>04:05:20</t>
+          <t>21:52:47</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2688,7 +2699,7 @@
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=862717486357582', 'commentId': '862717486357582', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3Xzg2MjcxNzQ4NjM1NzU4Mg==', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N184NjI3MTc0ODYzNTc1ODI=', 'date': '2026-06-11T04:05:20.000Z', 'text': 'Me vi este video tomando justo leche alpina 😂', 'author': {'__typename': 'User', 'id': 'pfbid0Bkdc</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=995084453485725', 'commentId': '995084453485725', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3Xzk5NTA4NDQ1MzQ4NTcyNQ==', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N185OTUwODQ0NTM0ODU3MjU=', 'date': '2026-06-11T21:52:47.000Z', 'text': 'Dios los maldiga por lo que le hacen a las vacas.', 'author': {'__typename': 'User', 'id': 'pfbid0</t>
         </is>
       </c>
     </row>
@@ -2714,23 +2725,23 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cristhian Castro</t>
+          <t>Me vi este video tomando justo leche alpina 😂</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-06-11T03:46:14.000Z</t>
+          <t>2026-06-11T04:05:20.000Z</t>
         </is>
       </c>
       <c r="H36" s="1" t="n">
-        <v>46184.15710648148</v>
+        <v>46184.17037037037</v>
       </c>
       <c r="I36" s="1" t="n">
         <v>46184</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>03:46:14</t>
+          <t>04:05:20</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2747,7 +2758,7 @@
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1650057302715364&amp;reply_comment_id=1670040630916580', 'commentId': '1650057302715364', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE2NzAwNDA2MzA5MTY1ODA=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNjcwMDQwNjMwOTE2NTgw', 'date': '2026-06-11T03:46:14.000Z', 'text': 'Cristhian Castro', 'author': {'__typename': 'User', '__isActor</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=862717486357582', 'commentId': '862717486357582', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3Xzg2MjcxNzQ4NjM1NzU4Mg==', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N184NjI3MTc0ODYzNTc1ODI=', 'date': '2026-06-11T04:05:20.000Z', 'text': 'Me vi este video tomando justo leche alpina 😂', 'author': {'__typename': 'User', 'id': 'pfbid0Bkdc</t>
         </is>
       </c>
     </row>
@@ -2773,23 +2784,23 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sin leche no existirá alpina ni el vaso de yogurt agua a 4 mil pesos</t>
+          <t>Cristhian Castro</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-06-11T02:35:14.000Z</t>
+          <t>2026-06-11T03:46:14.000Z</t>
         </is>
       </c>
       <c r="H37" s="1" t="n">
-        <v>46184.10780092593</v>
+        <v>46184.15710648148</v>
       </c>
       <c r="I37" s="1" t="n">
         <v>46184</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>02:35:14</t>
+          <t>03:46:14</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2806,7 +2817,7 @@
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=870232606134016', 'commentId': '870232606134016', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3Xzg3MDIzMjYwNjEzNDAxNg==', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N184NzAyMzI2MDYxMzQwMTY=', 'date': '2026-06-11T02:35:14.000Z', 'text': 'Sin leche no existirá alpina ni el vaso de yogurt agua a 4 mil pesos', 'author': {'__typename': 'U</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1650057302715364&amp;reply_comment_id=1670040630916580', 'commentId': '1650057302715364', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE2NzAwNDA2MzA5MTY1ODA=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNjcwMDQwNjMwOTE2NTgw', 'date': '2026-06-11T03:46:14.000Z', 'text': 'Cristhian Castro', 'author': {'__typename': 'User', '__isActor</t>
         </is>
       </c>
     </row>
@@ -2832,23 +2843,23 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Precio</t>
+          <t>Sin leche no existirá alpina ni el vaso de yogurt agua a 4 mil pesos</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-06-10T17:34:25.000Z</t>
+          <t>2026-06-11T02:35:14.000Z</t>
         </is>
       </c>
       <c r="H38" s="1" t="n">
-        <v>46183.7322337963</v>
+        <v>46184.10780092593</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>17:34:25</t>
+          <t>02:35:14</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2865,7 +2876,7 @@
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1936632696995303', 'commentId': '1936632696995303', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE5MzY2MzI2OTY5OTUzMDM=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xOTM2NjMyNjk2OTk1MzAz', 'date': '2026-06-10T17:34:25.000Z', 'text': 'Precio', 'author': {'__typename': 'User', 'id': 'pfbid06JFUdP8sNBsNxGLkG7PJ9JsCZ6z1spVq4nzq8q46i</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=870232606134016', 'commentId': '870232606134016', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3Xzg3MDIzMjYwNjEzNDAxNg==', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N184NzAyMzI2MDYxMzQwMTY=', 'date': '2026-06-11T02:35:14.000Z', 'text': 'Sin leche no existirá alpina ni el vaso de yogurt agua a 4 mil pesos', 'author': {'__typename': 'U</t>
         </is>
       </c>
     </row>
@@ -2891,23 +2902,23 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Para eso la mejor leche es la de cabrá.  La leche de vaca es cancerígenas dice el pueblo . Como vivian los antecesores  ja</t>
+          <t>Precio</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-06-10T15:34:45.000Z</t>
+          <t>2026-06-10T17:34:25.000Z</t>
         </is>
       </c>
       <c r="H39" s="1" t="n">
-        <v>46183.64913194445</v>
+        <v>46183.7322337963</v>
       </c>
       <c r="I39" s="1" t="n">
         <v>46183</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>15:34:45</t>
+          <t>17:34:25</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2924,7 +2935,7 @@
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr">
         <is>
-          <t xml:space="preserve">{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1763577697978693', 'commentId': '1763577697978693', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE3NjM1Nzc2OTc5Nzg2OTM=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNzYzNTc3Njk3OTc4Njkz', 'date': '2026-06-10T15:34:45.000Z', 'text': 'Para eso la mejor leche es la de cabrá.  La leche de vaca es cancerígenas dice el pueblo . Como </t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1936632696995303', 'commentId': '1936632696995303', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE5MzY2MzI2OTY5OTUzMDM=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xOTM2NjMyNjk2OTk1MzAz', 'date': '2026-06-10T17:34:25.000Z', 'text': 'Precio', 'author': {'__typename': 'User', 'id': 'pfbid06JFUdP8sNBsNxGLkG7PJ9JsCZ6z1spVq4nzq8q46i</t>
         </is>
       </c>
     </row>
@@ -2950,23 +2961,23 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>y esa mala cara que es</t>
+          <t>Para eso la mejor leche es la de cabrá.  La leche de vaca es cancerígenas dice el pueblo . Como vivian los antecesores  ja</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-06-09T21:17:04.000Z</t>
+          <t>2026-06-10T15:34:45.000Z</t>
         </is>
       </c>
       <c r="H40" s="1" t="n">
-        <v>46182.88685185185</v>
+        <v>46183.64913194445</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>21:17:04</t>
+          <t>15:34:45</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2983,7 +2994,7 @@
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1015387484765410', 'commentId': '1015387484765410', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEwMTUzODc0ODQ3NjU0MTA=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMDE1Mzg3NDg0NzY1NDEw', 'date': '2026-06-09T21:17:04.000Z', 'text': 'y esa mala cara que es', 'author': {'__typename': 'User', 'id': 'pfbid0yXRNeQ6URs5CBxdVUvs2x9XLQ</t>
+          <t xml:space="preserve">{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1763577697978693', 'commentId': '1763577697978693', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE3NjM1Nzc2OTc5Nzg2OTM=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNzYzNTc3Njk3OTc4Njkz', 'date': '2026-06-10T15:34:45.000Z', 'text': 'Para eso la mejor leche es la de cabrá.  La leche de vaca es cancerígenas dice el pueblo . Como </t>
         </is>
       </c>
     </row>
@@ -3009,23 +3020,23 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Esa leche solo le cambia el color a la mierda</t>
+          <t>y esa mala cara que es</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-06-08T23:04:28.000Z</t>
+          <t>2026-06-09T21:17:04.000Z</t>
         </is>
       </c>
       <c r="H41" s="1" t="n">
-        <v>46181.96143518519</v>
+        <v>46182.88685185185</v>
       </c>
       <c r="I41" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>23:04:28</t>
+          <t>21:17:04</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -3042,7 +3053,7 @@
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=2205697686864259', 'commentId': '2205697686864259', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzIyMDU2OTc2ODY4NjQyNTk=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18yMjA1Njk3Njg2ODY0MjU5', 'date': '2026-06-08T23:04:28.000Z', 'text': 'Esa leche solo le cambia el color a la mierda', 'author': {'__typename': 'User', 'id': 'pfbid02r</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1015387484765410', 'commentId': '1015387484765410', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEwMTUzODc0ODQ3NjU0MTA=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMDE1Mzg3NDg0NzY1NDEw', 'date': '2026-06-09T21:17:04.000Z', 'text': 'y esa mala cara que es', 'author': {'__typename': 'User', 'id': 'pfbid0yXRNeQ6URs5CBxdVUvs2x9XLQ</t>
         </is>
       </c>
     </row>
@@ -3068,23 +3079,23 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ABELARDO DE LA SPRIELLA PRESIDENTE</t>
+          <t>Esa leche solo le cambia el color a la mierda</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-06-08T21:05:06.000Z</t>
+          <t>2026-06-08T23:04:28.000Z</t>
         </is>
       </c>
       <c r="H42" s="1" t="n">
-        <v>46181.87854166667</v>
+        <v>46181.96143518519</v>
       </c>
       <c r="I42" s="1" t="n">
         <v>46181</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>21:05:06</t>
+          <t>23:04:28</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -3101,7 +3112,7 @@
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=943020682087299', 'commentId': '943020682087299', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3Xzk0MzAyMDY4MjA4NzI5OQ==', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N185NDMwMjA2ODIwODcyOTk=', 'date': '2026-06-08T21:05:06.000Z', 'text': 'ABELARDO DE LA SPRIELLA PRESIDENTE', 'author': {'__typename': 'User', 'id': 'pfbid02vjgMonnzExCrde</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=2205697686864259', 'commentId': '2205697686864259', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzIyMDU2OTc2ODY4NjQyNTk=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18yMjA1Njk3Njg2ODY0MjU5', 'date': '2026-06-08T23:04:28.000Z', 'text': 'Esa leche solo le cambia el color a la mierda', 'author': {'__typename': 'User', 'id': 'pfbid02r</t>
         </is>
       </c>
     </row>
@@ -3127,23 +3138,23 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Firmes</t>
+          <t>ABELARDO DE LA SPRIELLA PRESIDENTE</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-06-08T20:59:40.000Z</t>
+          <t>2026-06-08T21:05:06.000Z</t>
         </is>
       </c>
       <c r="H43" s="1" t="n">
-        <v>46181.87476851852</v>
+        <v>46181.87854166667</v>
       </c>
       <c r="I43" s="1" t="n">
         <v>46181</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>20:59:40</t>
+          <t>21:05:06</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -3160,7 +3171,7 @@
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1516416566587548', 'commentId': '1516416566587548', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE1MTY0MTY1NjY1ODc1NDg=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNTE2NDE2NTY2NTg3NTQ4', 'date': '2026-06-08T20:59:40.000Z', 'text': 'Firmes', 'author': {'__typename': 'User', 'id': 'pfbid033dc9dxdfw2m6VLbXXjTrk6YmJRRJEZK7hXJAJdxw</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=943020682087299', 'commentId': '943020682087299', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3Xzk0MzAyMDY4MjA4NzI5OQ==', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N185NDMwMjA2ODIwODcyOTk=', 'date': '2026-06-08T21:05:06.000Z', 'text': 'ABELARDO DE LA SPRIELLA PRESIDENTE', 'author': {'__typename': 'User', 'id': 'pfbid02vjgMonnzExCrde</t>
         </is>
       </c>
     </row>
@@ -3186,23 +3197,23 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Para mi la mejor leche es la de alpina</t>
+          <t>Firmes</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-06-08T20:09:49.000Z</t>
+          <t>2026-06-08T20:59:40.000Z</t>
         </is>
       </c>
       <c r="H44" s="1" t="n">
-        <v>46181.84015046297</v>
+        <v>46181.87476851852</v>
       </c>
       <c r="I44" s="1" t="n">
         <v>46181</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>20:09:49</t>
+          <t>20:59:40</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -3219,7 +3230,7 @@
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=2602426543545930', 'commentId': '2602426543545930', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzI2MDI0MjY1NDM1NDU5MzA=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18yNjAyNDI2NTQzNTQ1OTMw', 'date': '2026-06-08T20:09:49.000Z', 'text': 'Para mi la mejor leche es la de alpina', 'author': {'__typename': 'User', 'id': 'pfbid03JpnjYcm7</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1516416566587548', 'commentId': '1516416566587548', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE1MTY0MTY1NjY1ODc1NDg=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNTE2NDE2NTY2NTg3NTQ4', 'date': '2026-06-08T20:59:40.000Z', 'text': 'Firmes', 'author': {'__typename': 'User', 'id': 'pfbid033dc9dxdfw2m6VLbXXjTrk6YmJRRJEZK7hXJAJdxw</t>
         </is>
       </c>
     </row>
@@ -3245,27 +3256,27 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bienvenido a mi vida</t>
+          <t>Para mi la mejor leche es la de alpina</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-06-08T17:51:29.000Z</t>
+          <t>2026-06-08T20:09:49.000Z</t>
         </is>
       </c>
       <c r="H45" s="1" t="n">
-        <v>46181.74408564815</v>
+        <v>46181.84015046297</v>
       </c>
       <c r="I45" s="1" t="n">
         <v>46181</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>17:51:29</t>
+          <t>20:09:49</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -3278,7 +3289,7 @@
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1650057302715364', 'commentId': '1650057302715364', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE2NTAwNTczMDI3MTUzNjQ=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNjUwMDU3MzAyNzE1MzY0', 'date': '2026-06-08T17:51:29.000Z', 'text': 'Bienvenido a mi vida', 'author': {'__typename': 'User', 'id': '100003377225415', 'name': 'Cristh</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=2602426543545930', 'commentId': '2602426543545930', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzI2MDI0MjY1NDM1NDU5MzA=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18yNjAyNDI2NTQzNTQ1OTMw', 'date': '2026-06-08T20:09:49.000Z', 'text': 'Para mi la mejor leche es la de alpina', 'author': {'__typename': 'User', 'id': 'pfbid03JpnjYcm7</t>
         </is>
       </c>
     </row>
@@ -3304,27 +3315,27 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Leche esencial en la vida humana</t>
+          <t>Bienvenido a mi vida</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-06-08T17:44:38.000Z</t>
+          <t>2026-06-08T17:51:29.000Z</t>
         </is>
       </c>
       <c r="H46" s="1" t="n">
-        <v>46181.7393287037</v>
+        <v>46181.74408564815</v>
       </c>
       <c r="I46" s="1" t="n">
         <v>46181</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>17:44:38</t>
+          <t>17:51:29</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -3337,7 +3348,7 @@
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1656700515621731', 'commentId': '1656700515621731', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE2NTY3MDA1MTU2MjE3MzE=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNjU2NzAwNTE1NjIxNzMx', 'date': '2026-06-08T17:44:38.000Z', 'text': 'Leche esencial en la vida humana', 'author': {'__typename': 'User', 'id': 'pfbid02uS78LnA3epB5f8</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1650057302715364', 'commentId': '1650057302715364', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE2NTAwNTczMDI3MTUzNjQ=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNjUwMDU3MzAyNzE1MzY0', 'date': '2026-06-08T17:51:29.000Z', 'text': 'Bienvenido a mi vida', 'author': {'__typename': 'User', 'id': '100003377225415', 'name': 'Cristh</t>
         </is>
       </c>
     </row>
@@ -3363,23 +3374,23 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Me encanta gracias amigos</t>
+          <t>Leche esencial en la vida humana</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-06-08T02:04:42.000Z</t>
+          <t>2026-06-08T17:44:38.000Z</t>
         </is>
       </c>
       <c r="H47" s="1" t="n">
-        <v>46181.08659722222</v>
+        <v>46181.7393287037</v>
       </c>
       <c r="I47" s="1" t="n">
         <v>46181</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>02:04:42</t>
+          <t>17:44:38</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -3396,7 +3407,7 @@
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=4483457891876445', 'commentId': '4483457891876445', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzQ0ODM0NTc4OTE4NzY0NDU=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N180NDgzNDU3ODkxODc2NDQ1', 'date': '2026-06-08T02:04:42.000Z', 'text': 'Me encanta gracias amigos', 'author': {'__typename': 'User', 'id': 'pfbid0tSSiFkv74fS5gkHE3SLXx7</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1656700515621731', 'commentId': '1656700515621731', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE2NTY3MDA1MTU2MjE3MzE=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNjU2NzAwNTE1NjIxNzMx', 'date': '2026-06-08T17:44:38.000Z', 'text': 'Leche esencial en la vida humana', 'author': {'__typename': 'User', 'id': 'pfbid02uS78LnA3epB5f8</t>
         </is>
       </c>
     </row>
@@ -3422,23 +3433,23 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Si la leche de los hombres no salen preñadas las mujeres jajajajajajaa</t>
+          <t>Me encanta gracias amigos</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-06-07T12:58:30.000Z</t>
+          <t>2026-06-08T02:04:42.000Z</t>
         </is>
       </c>
       <c r="H48" s="1" t="n">
-        <v>46180.540625</v>
+        <v>46181.08659722222</v>
       </c>
       <c r="I48" s="1" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>12:58:30</t>
+          <t>02:04:42</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -3455,7 +3466,7 @@
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=2460021841186072', 'commentId': '2460021841186072', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzI0NjAwMjE4NDExODYwNzI=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18yNDYwMDIxODQxMTg2MDcy', 'date': '2026-06-07T12:58:30.000Z', 'text': 'Si la leche de los hombres no salen preñadas las mujeres jajajajajajaa', 'author': {'__typename'</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=4483457891876445', 'commentId': '4483457891876445', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzQ0ODM0NTc4OTE4NzY0NDU=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N180NDgzNDU3ODkxODc2NDQ1', 'date': '2026-06-08T02:04:42.000Z', 'text': 'Me encanta gracias amigos', 'author': {'__typename': 'User', 'id': 'pfbid0tSSiFkv74fS5gkHE3SLXx7</t>
         </is>
       </c>
     </row>
@@ -3481,23 +3492,23 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Y de dónde sale la leche, de las vacas y de dónde salen la vacas del campo, y quien quiere meterle veneno a la tierra con el fracking si aguevardo firme por traicionar a la patria</t>
+          <t>Si la leche de los hombres no salen preñadas las mujeres jajajajajajaa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-06-06T18:14:51.000Z</t>
+          <t>2026-06-07T12:58:30.000Z</t>
         </is>
       </c>
       <c r="H49" s="1" t="n">
-        <v>46179.7603125</v>
+        <v>46180.540625</v>
       </c>
       <c r="I49" s="1" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>18:14:51</t>
+          <t>12:58:30</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -3514,7 +3525,7 @@
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1536768038124120', 'commentId': '1536768038124120', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE1MzY3NjgwMzgxMjQxMjA=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNTM2NzY4MDM4MTI0MTIw', 'date': '2026-06-06T18:14:51.000Z', 'text': 'Y de dónde sale la leche, de las vacas y de dónde salen la vacas del campo, y quien quiere meter</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=2460021841186072', 'commentId': '2460021841186072', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzI0NjAwMjE4NDExODYwNzI=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18yNDYwMDIxODQxMTg2MDcy', 'date': '2026-06-07T12:58:30.000Z', 'text': 'Si la leche de los hombres no salen preñadas las mujeres jajajajajajaa', 'author': {'__typename'</t>
         </is>
       </c>
     </row>
@@ -3540,23 +3551,23 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>PRESIDENTE PERO DE LA JUNTA DE ACCION COMUNAL DE MI BARRIO</t>
+          <t>Y de dónde sale la leche, de las vacas y de dónde salen la vacas del campo, y quien quiere meterle veneno a la tierra con el fracking si aguevardo firme por traicionar a la patria</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-06-06T03:04:25.000Z</t>
+          <t>2026-06-06T18:14:51.000Z</t>
         </is>
       </c>
       <c r="H50" s="1" t="n">
-        <v>46179.12806712963</v>
+        <v>46179.7603125</v>
       </c>
       <c r="I50" s="1" t="n">
         <v>46179</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>03:04:25</t>
+          <t>18:14:51</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -3573,7 +3584,7 @@
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1546422746896400', 'commentId': '1546422746896400', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE1NDY0MjI3NDY4OTY0MDA=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNTQ2NDIyNzQ2ODk2NDAw', 'date': '2026-06-06T03:04:25.000Z', 'text': 'PRESIDENTE PERO DE LA JUNTA DE ACCION COMUNAL DE MI BARRIO', 'author': {'__typename': 'User', 'i</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1536768038124120', 'commentId': '1536768038124120', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE1MzY3NjgwMzgxMjQxMjA=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNTM2NzY4MDM4MTI0MTIw', 'date': '2026-06-06T18:14:51.000Z', 'text': 'Y de dónde sale la leche, de las vacas y de dónde salen la vacas del campo, y quien quiere meter</t>
         </is>
       </c>
     </row>
@@ -3599,23 +3610,23 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Que paso con la avena deslactosada?</t>
+          <t>PRESIDENTE PERO DE LA JUNTA DE ACCION COMUNAL DE MI BARRIO</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-06-06T01:38:41.000Z</t>
+          <t>2026-06-06T03:04:25.000Z</t>
         </is>
       </c>
       <c r="H51" s="1" t="n">
-        <v>46179.06853009259</v>
+        <v>46179.12806712963</v>
       </c>
       <c r="I51" s="1" t="n">
         <v>46179</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>01:38:41</t>
+          <t>03:04:25</t>
         </is>
       </c>
       <c r="K51" t="n">
@@ -3632,7 +3643,7 @@
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1980454275946084', 'commentId': '1980454275946084', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE5ODA0NTQyNzU5NDYwODQ=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xOTgwNDU0Mjc1OTQ2MDg0', 'date': '2026-06-06T01:38:41.000Z', 'text': 'Que paso con la avena deslactosada?', 'author': {'__typename': 'User', 'id': 'pfbid03kGevmUFRf8G</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1546422746896400', 'commentId': '1546422746896400', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE1NDY0MjI3NDY4OTY0MDA=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNTQ2NDIyNzQ2ODk2NDAw', 'date': '2026-06-06T03:04:25.000Z', 'text': 'PRESIDENTE PERO DE LA JUNTA DE ACCION COMUNAL DE MI BARRIO', 'author': {'__typename': 'User', 'i</t>
         </is>
       </c>
     </row>
@@ -3658,27 +3669,27 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dios hizo todo perfecto.</t>
+          <t>Que paso con la avena deslactosada?</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-06-05T23:04:25.000Z</t>
+          <t>2026-06-06T01:38:41.000Z</t>
         </is>
       </c>
       <c r="H52" s="1" t="n">
-        <v>46178.96140046296</v>
+        <v>46179.06853009259</v>
       </c>
       <c r="I52" s="1" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>23:04:25</t>
+          <t>01:38:41</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -3691,7 +3702,7 @@
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=2220326995402183', 'commentId': '2220326995402183', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzIyMjAzMjY5OTU0MDIxODM=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18yMjIwMzI2OTk1NDAyMTgz', 'date': '2026-06-05T23:04:25.000Z', 'text': 'Dios hizo todo perfecto.', 'author': {'__typename': 'User', 'id': 'pfbid02uErgUfnAByUnNENfqqduqh</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1980454275946084', 'commentId': '1980454275946084', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE5ODA0NTQyNzU5NDYwODQ=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xOTgwNDU0Mjc1OTQ2MDg0', 'date': '2026-06-06T01:38:41.000Z', 'text': 'Que paso con la avena deslactosada?', 'author': {'__typename': 'User', 'id': 'pfbid03kGevmUFRf8G</t>
         </is>
       </c>
     </row>
@@ -3717,27 +3728,27 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Por eso le pagan a 1400 el litro de leche a los campesinos, porque les interesa el campo. Hipócritas avaros</t>
+          <t>Dios hizo todo perfecto.</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-06-05T22:56:31.000Z</t>
+          <t>2026-06-05T23:04:25.000Z</t>
         </is>
       </c>
       <c r="H53" s="1" t="n">
-        <v>46178.95591435185</v>
+        <v>46178.96140046296</v>
       </c>
       <c r="I53" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>22:56:31</t>
+          <t>23:04:25</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -3750,7 +3761,7 @@
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1466980861417379', 'commentId': '1466980861417379', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE0NjY5ODA4NjE0MTczNzk=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNDY2OTgwODYxNDE3Mzc5', 'date': '2026-06-05T22:56:31.000Z', 'text': 'Por eso le pagan a 1400 el litro de leche a los campesinos, porque les interesa el campo. Hipócr</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=2220326995402183', 'commentId': '2220326995402183', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzIyMjAzMjY5OTU0MDIxODM=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18yMjIwMzI2OTk1NDAyMTgz', 'date': '2026-06-05T23:04:25.000Z', 'text': 'Dios hizo todo perfecto.', 'author': {'__typename': 'User', 'id': 'pfbid02uErgUfnAByUnNENfqqduqh</t>
         </is>
       </c>
     </row>
@@ -3776,27 +3787,27 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Seríamos más sanos.</t>
+          <t>Por eso le pagan a 1400 el litro de leche a los campesinos, porque les interesa el campo. Hipócritas avaros</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-06-05T21:32:08.000Z</t>
+          <t>2026-06-05T22:56:31.000Z</t>
         </is>
       </c>
       <c r="H54" s="1" t="n">
-        <v>46178.89731481481</v>
+        <v>46178.95591435185</v>
       </c>
       <c r="I54" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>21:32:08</t>
+          <t>22:56:31</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -3809,7 +3820,7 @@
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1321750493434078', 'commentId': '1321750493434078', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEzMjE3NTA0OTM0MzQwNzg=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMzIxNzUwNDkzNDM0MDc4', 'date': '2026-06-05T21:32:08.000Z', 'text': 'Seríamos más sanos.', 'author': {'__typename': 'User', 'id': 'pfbid0211v2PgCsriu7ZieBTqNBdTzxeMs</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1466980861417379', 'commentId': '1466980861417379', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE0NjY5ODA4NjE0MTczNzk=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNDY2OTgwODYxNDE3Mzc5', 'date': '2026-06-05T22:56:31.000Z', 'text': 'Por eso le pagan a 1400 el litro de leche a los campesinos, porque les interesa el campo. Hipócr</t>
         </is>
       </c>
     </row>
@@ -3835,27 +3846,27 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Leche o lactosuero es escurridura con saborizantes</t>
+          <t>Seríamos más sanos.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-06-05T19:40:16.000Z</t>
+          <t>2026-06-05T21:32:08.000Z</t>
         </is>
       </c>
       <c r="H55" s="1" t="n">
-        <v>46178.81962962963</v>
+        <v>46178.89731481481</v>
       </c>
       <c r="I55" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>19:40:16</t>
+          <t>21:32:08</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -3868,7 +3879,7 @@
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1742474310293914', 'commentId': '1742474310293914', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE3NDI0NzQzMTAyOTM5MTQ=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNzQyNDc0MzEwMjkzOTE0', 'date': '2026-06-05T19:40:16.000Z', 'text': 'Leche o lactosuero es escurridura con saborizantes', 'author': {'__typename': 'User', 'id': 'pfb</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1321750493434078', 'commentId': '1321750493434078', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEzMjE3NTA0OTM0MzQwNzg=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMzIxNzUwNDkzNDM0MDc4', 'date': '2026-06-05T21:32:08.000Z', 'text': 'Seríamos más sanos.', 'author': {'__typename': 'User', 'id': 'pfbid0211v2PgCsriu7ZieBTqNBdTzxeMs</t>
         </is>
       </c>
     </row>
@@ -3894,27 +3905,27 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Policías en cada mesa de votación para que prohíba el uso de celular porque toman foto y luego van a cobrar eso es fraude prohibido el uso del celular en la mesa de votación</t>
+          <t>Leche o lactosuero es escurridura con saborizantes</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-06-05T18:36:29.000Z</t>
+          <t>2026-06-05T19:40:16.000Z</t>
         </is>
       </c>
       <c r="H56" s="1" t="n">
-        <v>46178.77533564815</v>
+        <v>46178.81962962963</v>
       </c>
       <c r="I56" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>18:36:29</t>
+          <t>19:40:16</t>
         </is>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -3927,7 +3938,7 @@
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=807045099006490', 'commentId': '807045099006490', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzgwNzA0NTA5OTAwNjQ5MA==', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N184MDcwNDUwOTkwMDY0OTA=', 'date': '2026-06-05T18:36:29.000Z', 'text': 'Policías en cada mesa de votación para que prohíba el uso de celular porque toman foto y luego van</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1742474310293914', 'commentId': '1742474310293914', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE3NDI0NzQzMTAyOTM5MTQ=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNzQyNDc0MzEwMjkzOTE0', 'date': '2026-06-05T19:40:16.000Z', 'text': 'Leche o lactosuero es escurridura con saborizantes', 'author': {'__typename': 'User', 'id': 'pfb</t>
         </is>
       </c>
     </row>
@@ -3953,23 +3964,23 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Una vida sin leche sería más saludable..</t>
+          <t>Policías en cada mesa de votación para que prohíba el uso de celular porque toman foto y luego van a cobrar eso es fraude prohibido el uso del celular en la mesa de votación</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-06-05T15:45:53.000Z</t>
+          <t>2026-06-05T18:36:29.000Z</t>
         </is>
       </c>
       <c r="H57" s="1" t="n">
-        <v>46178.65686342592</v>
+        <v>46178.77533564815</v>
       </c>
       <c r="I57" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>15:45:53</t>
+          <t>18:36:29</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -3986,7 +3997,7 @@
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1613621236403186', 'commentId': '1613621236403186', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE2MTM2MjEyMzY0MDMxODY=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNjEzNjIxMjM2NDAzMTg2', 'date': '2026-06-05T15:45:53.000Z', 'text': 'Una vida sin leche sería más saludable..', 'author': {'__typename': 'User', 'id': 'pfbid0221FUN5</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=807045099006490', 'commentId': '807045099006490', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzgwNzA0NTA5OTAwNjQ5MA==', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N184MDcwNDUwOTkwMDY0OTA=', 'date': '2026-06-05T18:36:29.000Z', 'text': 'Policías en cada mesa de votación para que prohíba el uso de celular porque toman foto y luego van</t>
         </is>
       </c>
     </row>
@@ -4012,27 +4023,27 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Trabajadora</t>
+          <t>Una vida sin leche sería más saludable..</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-06-05T13:06:49.000Z</t>
+          <t>2026-06-05T15:45:53.000Z</t>
         </is>
       </c>
       <c r="H58" s="1" t="n">
-        <v>46178.54640046296</v>
+        <v>46178.65686342592</v>
       </c>
       <c r="I58" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>13:06:49</t>
+          <t>15:45:53</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -4045,7 +4056,7 @@
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=999855859294373', 'commentId': '999855859294373', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3Xzk5OTg1NTg1OTI5NDM3Mw==', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N185OTk4NTU4NTkyOTQzNzM=', 'date': '2026-06-05T13:06:49.000Z', 'text': 'Trabajadora', 'author': {'__typename': 'User', 'id': 'pfbid02xhav5AyvXr1QckJZhRiRiWLGAWcNSdMDKjxHR</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1613621236403186', 'commentId': '1613621236403186', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE2MTM2MjEyMzY0MDMxODY=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNjEzNjIxMjM2NDAzMTg2', 'date': '2026-06-05T15:45:53.000Z', 'text': 'Una vida sin leche sería más saludable..', 'author': {'__typename': 'User', 'id': 'pfbid0221FUN5</t>
         </is>
       </c>
     </row>
@@ -4071,27 +4082,27 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Un delicioso chocolate con azucar y con leche...y almojabanita...que rico, ...un dulce abrazo Sabina</t>
+          <t>Trabajadora</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-06-05T11:07:42.000Z</t>
+          <t>2026-06-05T13:06:49.000Z</t>
         </is>
       </c>
       <c r="H59" s="1" t="n">
-        <v>46178.46368055556</v>
+        <v>46178.54640046296</v>
       </c>
       <c r="I59" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>11:07:42</t>
+          <t>13:06:49</t>
         </is>
       </c>
       <c r="K59" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -4104,7 +4115,7 @@
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=4495969137304720', 'commentId': '4495969137304720', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzQ0OTU5NjkxMzczMDQ3MjA=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N180NDk1OTY5MTM3MzA0NzIw', 'date': '2026-06-05T11:07:42.000Z', 'text': 'Un delicioso chocolate con azucar y con leche...y almojabanita...que rico, ...un dulce abrazo Sa</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=999855859294373', 'commentId': '999855859294373', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3Xzk5OTg1NTg1OTI5NDM3Mw==', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N185OTk4NTU4NTkyOTQzNzM=', 'date': '2026-06-05T13:06:49.000Z', 'text': 'Trabajadora', 'author': {'__typename': 'User', 'id': 'pfbid02xhav5AyvXr1QckJZhRiRiWLGAWcNSdMDKjxHR</t>
         </is>
       </c>
     </row>
@@ -4130,27 +4141,27 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Después que no me falte leche en las bolas</t>
+          <t>Un delicioso chocolate con azucar y con leche...y almojabanita...que rico, ...un dulce abrazo Sabina</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-06-04T17:56:00.000Z</t>
+          <t>2026-06-05T11:07:42.000Z</t>
         </is>
       </c>
       <c r="H60" s="1" t="n">
-        <v>46177.74722222222</v>
+        <v>46178.46368055556</v>
       </c>
       <c r="I60" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>17:56:00</t>
+          <t>11:07:42</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -4163,7 +4174,7 @@
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=967627006156085', 'commentId': '967627006156085', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3Xzk2NzYyNzAwNjE1NjA4NQ==', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N185Njc2MjcwMDYxNTYwODU=', 'date': '2026-06-04T17:56:00.000Z', 'text': 'Después que no me falte leche en las bolas', 'author': {'__typename': 'User', 'id': 'pfbid0dTnbRjk</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=4495969137304720', 'commentId': '4495969137304720', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzQ0OTU5NjkxMzczMDQ3MjA=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N180NDk1OTY5MTM3MzA0NzIw', 'date': '2026-06-05T11:07:42.000Z', 'text': 'Un delicioso chocolate con azucar y con leche...y almojabanita...que rico, ...un dulce abrazo Sa</t>
         </is>
       </c>
     </row>
@@ -4189,23 +4200,23 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dulomoco, dulzaina, duque, Dumas, Dumoriez, ducal, durante, dureza, durmiente, dubitación, duna, duma.</t>
+          <t>Después que no me falte leche en las bolas</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-06-04T15:13:40.000Z</t>
+          <t>2026-06-04T17:56:00.000Z</t>
         </is>
       </c>
       <c r="H61" s="1" t="n">
-        <v>46177.63449074074</v>
+        <v>46177.74722222222</v>
       </c>
       <c r="I61" s="1" t="n">
         <v>46177</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>15:13:40</t>
+          <t>17:56:00</t>
         </is>
       </c>
       <c r="K61" t="n">
@@ -4222,7 +4233,7 @@
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=4360313190905352', 'commentId': '4360313190905352', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzQzNjAzMTMxOTA5MDUzNTI=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N180MzYwMzEzMTkwOTA1MzUy', 'date': '2026-06-04T15:13:40.000Z', 'text': 'Dulomoco, dulzaina, duque, Dumas, Dumoriez, ducal, durante, dureza, durmiente, dubitación, duna,</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=967627006156085', 'commentId': '967627006156085', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3Xzk2NzYyNzAwNjE1NjA4NQ==', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N185Njc2MjcwMDYxNTYwODU=', 'date': '2026-06-04T17:56:00.000Z', 'text': 'Después que no me falte leche en las bolas', 'author': {'__typename': 'User', 'id': 'pfbid0dTnbRjk</t>
         </is>
       </c>
     </row>
@@ -4248,23 +4259,23 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cuanto le dieron por decir babosadas malparido comiendo mierda ,bien llevado que estara y se vende por un tamal</t>
+          <t>Dulomoco, dulzaina, duque, Dumas, Dumoriez, ducal, durante, dureza, durmiente, dubitación, duna, duma.</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-06-04T12:54:09.000Z</t>
+          <t>2026-06-04T15:13:40.000Z</t>
         </is>
       </c>
       <c r="H62" s="1" t="n">
-        <v>46177.53760416667</v>
+        <v>46177.63449074074</v>
       </c>
       <c r="I62" s="1" t="n">
         <v>46177</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>12:54:09</t>
+          <t>15:13:40</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -4281,7 +4292,7 @@
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1801806774117258', 'commentId': '1801806774117258', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE4MDE4MDY3NzQxMTcyNTg=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xODAxODA2Nzc0MTE3MjU4', 'date': '2026-06-04T12:54:09.000Z', 'text': 'Cuanto le dieron por decir babosadas malparido comiendo mierda ,bien llevado que estara y se ven</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=4360313190905352', 'commentId': '4360313190905352', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzQzNjAzMTMxOTA5MDUzNTI=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N180MzYwMzEzMTkwOTA1MzUy', 'date': '2026-06-04T15:13:40.000Z', 'text': 'Dulomoco, dulzaina, duque, Dumas, Dumoriez, ducal, durante, dureza, durmiente, dubitación, duna,</t>
         </is>
       </c>
     </row>
@@ -4307,23 +4318,23 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Claudia Patricia Marcillo Patiño Mi razón si tiene argumentos señora, a diferencia de sus posturas sin fundamento... Le dicen no al Fracking y hablan de ambientalismo cuando van en carro y básicamente no brincan cuando hay otras acciones mucho más contaminantes las cuales según ustedes son una solución sostenible...</t>
+          <t>Cuanto le dieron por decir babosadas malparido comiendo mierda ,bien llevado que estara y se vende por un tamal</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-06-04T03:34:37.000Z</t>
+          <t>2026-06-04T12:54:09.000Z</t>
         </is>
       </c>
       <c r="H63" s="1" t="n">
-        <v>46177.14903935185</v>
+        <v>46177.53760416667</v>
       </c>
       <c r="I63" s="1" t="n">
         <v>46177</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>03:34:37</t>
+          <t>12:54:09</t>
         </is>
       </c>
       <c r="K63" t="n">
@@ -4340,7 +4351,7 @@
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr">
         <is>
-          <t xml:space="preserve">{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1018920390530674&amp;reply_comment_id=1071203365579173', 'commentId': '1018920390530674', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEwNzEyMDMzNjU1NzkxNzM=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMDcxMjAzMzY1NTc5MTcz', 'date': '2026-06-04T03:34:37.000Z', 'text': 'Claudia Patricia Marcillo Patiño Mi razón si tiene argumentos </t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1801806774117258', 'commentId': '1801806774117258', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE4MDE4MDY3NzQxMTcyNTg=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xODAxODA2Nzc0MTE3MjU4', 'date': '2026-06-04T12:54:09.000Z', 'text': 'Cuanto le dieron por decir babosadas malparido comiendo mierda ,bien llevado que estara y se ven</t>
         </is>
       </c>
     </row>
@@ -4366,23 +4377,23 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Se Imagina  que les quitan las Distribuidoras a  los distribuidores y  A los empleados les  Roban las liquidaciones  y las semanas de cotización a pensión</t>
+          <t>Claudia Patricia Marcillo Patiño Mi razón si tiene argumentos señora, a diferencia de sus posturas sin fundamento... Le dicen no al Fracking y hablan de ambientalismo cuando van en carro y básicamente no brincan cuando hay otras acciones mucho más contaminantes las cuales según ustedes son una solución sostenible...</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-06-03T23:46:58.000Z</t>
+          <t>2026-06-04T03:34:37.000Z</t>
         </is>
       </c>
       <c r="H64" s="1" t="n">
-        <v>46176.99094907408</v>
+        <v>46177.14903935185</v>
       </c>
       <c r="I64" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>23:46:58</t>
+          <t>03:34:37</t>
         </is>
       </c>
       <c r="K64" t="n">
@@ -4399,7 +4410,7 @@
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1324424726460303', 'commentId': '1324424726460303', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEzMjQ0MjQ3MjY0NjAzMDM=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMzI0NDI0NzI2NDYwMzAz', 'date': '2026-06-03T23:46:58.000Z', 'text': 'Se Imagina  que les quitan las Distribuidoras a  los distribuidores y  A los empleados les  Roba</t>
+          <t xml:space="preserve">{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1018920390530674&amp;reply_comment_id=1071203365579173', 'commentId': '1018920390530674', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEwNzEyMDMzNjU1NzkxNzM=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMDcxMjAzMzY1NTc5MTcz', 'date': '2026-06-04T03:34:37.000Z', 'text': 'Claudia Patricia Marcillo Patiño Mi razón si tiene argumentos </t>
         </is>
       </c>
     </row>
@@ -4425,23 +4436,23 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Juan David Restrepo de razón tu postura política te falta decir q lo tienes grande ese es el nivel de conocimiento de Abelardo y sus seguidores👌a falta de conocimiento el insulto se convierte en la mejor arma los pobres de derecha🙄</t>
+          <t>Se Imagina  que les quitan las Distribuidoras a  los distribuidores y  A los empleados les  Roban las liquidaciones  y las semanas de cotización a pensión</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-06-03T21:56:39.000Z</t>
+          <t>2026-06-03T23:46:58.000Z</t>
         </is>
       </c>
       <c r="H65" s="1" t="n">
-        <v>46176.91434027778</v>
+        <v>46176.99094907408</v>
       </c>
       <c r="I65" s="1" t="n">
         <v>46176</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>21:56:39</t>
+          <t>23:46:58</t>
         </is>
       </c>
       <c r="K65" t="n">
@@ -4458,7 +4469,7 @@
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1018920390530674&amp;reply_comment_id=4555030531385501', 'commentId': '1018920390530674', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzQ1NTUwMzA1MzEzODU1MDE=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N180NTU1MDMwNTMxMzg1NTAx', 'date': '2026-06-03T21:56:39.000Z', 'text': 'Juan David Restrepo de razón tu postura política te falta deci</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1324424726460303', 'commentId': '1324424726460303', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEzMjQ0MjQ3MjY0NjAzMDM=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMzI0NDI0NzI2NDYwMzAz', 'date': '2026-06-03T23:46:58.000Z', 'text': 'Se Imagina  que les quitan las Distribuidoras a  los distribuidores y  A los empleados les  Roba</t>
         </is>
       </c>
     </row>
@@ -4484,23 +4495,23 @@
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>La leche es un veneno para el ser humano. El queso no Pero la leche sí</t>
+          <t>Juan David Restrepo de razón tu postura política te falta decir q lo tienes grande ese es el nivel de conocimiento de Abelardo y sus seguidores👌a falta de conocimiento el insulto se convierte en la mejor arma los pobres de derecha🙄</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-06-03T17:29:55.000Z</t>
+          <t>2026-06-03T21:56:39.000Z</t>
         </is>
       </c>
       <c r="H66" s="1" t="n">
-        <v>46176.72910879629</v>
+        <v>46176.91434027778</v>
       </c>
       <c r="I66" s="1" t="n">
         <v>46176</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>17:29:55</t>
+          <t>21:56:39</t>
         </is>
       </c>
       <c r="K66" t="n">
@@ -4517,7 +4528,7 @@
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=2434426847025249', 'commentId': '2434426847025249', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzI0MzQ0MjY4NDcwMjUyNDk=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18yNDM0NDI2ODQ3MDI1MjQ5', 'date': '2026-06-03T17:29:55.000Z', 'text': 'La leche es un veneno para el ser humano. El queso no Pero la leche sí', 'author': {'__typename'</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1018920390530674&amp;reply_comment_id=4555030531385501', 'commentId': '1018920390530674', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzQ1NTUwMzA1MzEzODU1MDE=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N180NTU1MDMwNTMxMzg1NTAx', 'date': '2026-06-03T21:56:39.000Z', 'text': 'Juan David Restrepo de razón tu postura política te falta deci</t>
         </is>
       </c>
     </row>
@@ -4543,23 +4554,23 @@
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Pues vayase que falta no hace. Esta demorado en abandonar el Pais de la Belleza que ud ensucia. Chao geton</t>
+          <t>La leche es un veneno para el ser humano. El queso no Pero la leche sí</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-06-03T16:44:57.000Z</t>
+          <t>2026-06-03T17:29:55.000Z</t>
         </is>
       </c>
       <c r="H67" s="1" t="n">
-        <v>46176.69788194444</v>
+        <v>46176.72910879629</v>
       </c>
       <c r="I67" s="1" t="n">
         <v>46176</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>16:44:57</t>
+          <t>17:29:55</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -4576,7 +4587,7 @@
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr">
         <is>
-          <t xml:space="preserve">{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1248903487119558', 'commentId': '1248903487119558', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEyNDg5MDM0ODcxMTk1NTg=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMjQ4OTAzNDg3MTE5NTU4', 'date': '2026-06-03T16:44:57.000Z', 'text': 'Pues vayase que falta no hace. Esta demorado en abandonar el Pais de la Belleza que ud ensucia. </t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=2434426847025249', 'commentId': '2434426847025249', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzI0MzQ0MjY4NDcwMjUyNDk=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18yNDM0NDI2ODQ3MDI1MjQ5', 'date': '2026-06-03T17:29:55.000Z', 'text': 'La leche es un veneno para el ser humano. El queso no Pero la leche sí', 'author': {'__typename'</t>
         </is>
       </c>
     </row>
@@ -4602,27 +4613,27 @@
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Claudia Patricia Marcillo Patiño No se le ha quitado la Urticaria?? Fue tanto el ardor de jopo que todavía le anda rascando?</t>
+          <t>Pues vayase que falta no hace. Esta demorado en abandonar el Pais de la Belleza que ud ensucia. Chao geton</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-06-03T03:44:06.000Z</t>
+          <t>2026-06-03T16:44:57.000Z</t>
         </is>
       </c>
       <c r="H68" s="1" t="n">
-        <v>46176.155625</v>
+        <v>46176.69788194444</v>
       </c>
       <c r="I68" s="1" t="n">
         <v>46176</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>03:44:06</t>
+          <t>16:44:57</t>
         </is>
       </c>
       <c r="K68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -4635,7 +4646,7 @@
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1018920390530674&amp;reply_comment_id=977093231802746', 'commentId': '1018920390530674', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3Xzk3NzA5MzIzMTgwMjc0Ng==', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N185NzcwOTMyMzE4MDI3NDY=', 'date': '2026-06-03T03:44:06.000Z', 'text': 'Claudia Patricia Marcillo Patiño No se le ha quitado la Urticar</t>
+          <t xml:space="preserve">{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1248903487119558', 'commentId': '1248903487119558', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEyNDg5MDM0ODcxMTk1NTg=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMjQ4OTAzNDg3MTE5NTU4', 'date': '2026-06-03T16:44:57.000Z', 'text': 'Pues vayase que falta no hace. Esta demorado en abandonar el Pais de la Belleza que ud ensucia. </t>
         </is>
       </c>
     </row>
@@ -4661,27 +4672,27 @@
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sin agua no hay vida y así votan por el que va hacer fracking 🙄</t>
+          <t>Claudia Patricia Marcillo Patiño No se le ha quitado la Urticaria?? Fue tanto el ardor de jopo que todavía le anda rascando?</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-06-03T03:25:17.000Z</t>
+          <t>2026-06-03T03:44:06.000Z</t>
         </is>
       </c>
       <c r="H69" s="1" t="n">
-        <v>46176.14255787037</v>
+        <v>46176.155625</v>
       </c>
       <c r="I69" s="1" t="n">
         <v>46176</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>03:25:17</t>
+          <t>03:44:06</t>
         </is>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -4694,7 +4705,7 @@
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1018920390530674', 'commentId': '1018920390530674', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEwMTg5MjAzOTA1MzA2NzQ=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMDE4OTIwMzkwNTMwNjc0', 'date': '2026-06-03T03:25:17.000Z', 'text': 'Sin agua no hay vida y así votan por el que va hacer fracking 🙄', 'author': {'__typename': 'User</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1018920390530674&amp;reply_comment_id=977093231802746', 'commentId': '1018920390530674', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3Xzk3NzA5MzIzMTgwMjc0Ng==', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N185NzcwOTMyMzE4MDI3NDY=', 'date': '2026-06-03T03:44:06.000Z', 'text': 'Claudia Patricia Marcillo Patiño No se le ha quitado la Urticar</t>
         </is>
       </c>
     </row>
@@ -4720,23 +4731,23 @@
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sin leche hay lactosuero... Y con lactosuero hay mas campesinos estafados con tus precios Alpina</t>
+          <t>Sin agua no hay vida y así votan por el que va hacer fracking 🙄</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-06-03T01:15:06.000Z</t>
+          <t>2026-06-03T03:25:17.000Z</t>
         </is>
       </c>
       <c r="H70" s="1" t="n">
-        <v>46176.05215277777</v>
+        <v>46176.14255787037</v>
       </c>
       <c r="I70" s="1" t="n">
         <v>46176</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>01:15:06</t>
+          <t>03:25:17</t>
         </is>
       </c>
       <c r="K70" t="n">
@@ -4753,7 +4764,7 @@
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1014454464368440', 'commentId': '1014454464368440', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEwMTQ0NTQ0NjQzNjg0NDA=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMDE0NDU0NDY0MzY4NDQw', 'date': '2026-06-03T01:15:06.000Z', 'text': 'Sin leche hay lactosuero... Y con lactosuero hay mas campesinos estafados con tus precios Alpina</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1018920390530674', 'commentId': '1018920390530674', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEwMTg5MjAzOTA1MzA2NzQ=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMDE4OTIwMzkwNTMwNjc0', 'date': '2026-06-03T03:25:17.000Z', 'text': 'Sin agua no hay vida y así votan por el que va hacer fracking 🙄', 'author': {'__typename': 'User</t>
         </is>
       </c>
     </row>
@@ -4779,27 +4790,27 @@
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>No viviría inflamado, cero pedos.</t>
+          <t>Sin leche hay lactosuero... Y con lactosuero hay mas campesinos estafados con tus precios Alpina</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-06-03T01:14:10.000Z</t>
+          <t>2026-06-03T01:15:06.000Z</t>
         </is>
       </c>
       <c r="H71" s="1" t="n">
-        <v>46176.05150462963</v>
+        <v>46176.05215277777</v>
       </c>
       <c r="I71" s="1" t="n">
         <v>46176</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>01:14:10</t>
+          <t>01:15:06</t>
         </is>
       </c>
       <c r="K71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
@@ -4812,7 +4823,7 @@
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1007770421655962', 'commentId': '1007770421655962', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEwMDc3NzA0MjE2NTU5NjI=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMDA3NzcwNDIxNjU1OTYy', 'date': '2026-06-03T01:14:10.000Z', 'text': 'No viviría inflamado, cero pedos.', 'author': {'__typename': 'User', 'id': 'pfbid0efuAd5w8fZgz6m</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1014454464368440', 'commentId': '1014454464368440', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEwMTQ0NTQ0NjQzNjg0NDA=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMDE0NDU0NDY0MzY4NDQw', 'date': '2026-06-03T01:15:06.000Z', 'text': 'Sin leche hay lactosuero... Y con lactosuero hay mas campesinos estafados con tus precios Alpina</t>
         </is>
       </c>
     </row>
@@ -4838,27 +4849,27 @@
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Oralia orania odilia osneli Olivia oliva Osmani olimpia olimpa Odalis</t>
+          <t>No viviría inflamado, cero pedos.</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-06-02T18:39:17.000Z</t>
+          <t>2026-06-03T01:14:10.000Z</t>
         </is>
       </c>
       <c r="H72" s="1" t="n">
-        <v>46175.7772800926</v>
+        <v>46176.05150462963</v>
       </c>
       <c r="I72" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>18:39:17</t>
+          <t>01:14:10</t>
         </is>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
@@ -4870,6 +4881,65 @@
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1007770421655962', 'commentId': '1007770421655962', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzEwMDc3NzA0MjE2NTU5NjI=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xMDA3NzcwNDIxNjU1OTYy', 'date': '2026-06-03T01:14:10.000Z', 'text': 'No viviría inflamado, cero pedos.', 'author': {'__typename': 'User', 'id': 'pfbid0efuAd5w8fZgz6m</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>2</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/videos/4360112530867757</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Oralia orania odilia osneli Olivia oliva Osmani olimpia olimpa Odalis</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2026-06-02T18:39:17.000Z</t>
+        </is>
+      </c>
+      <c r="H73" s="1" t="n">
+        <v>46175.7772800926</v>
+      </c>
+      <c r="I73" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>18:39:17</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="b">
+        <v>0</v>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/videos/4360112530867757', 'commentUrl': 'https://www.facebook.com/alpina/videos/4360112530867757/?comment_id=1532475761552597', 'commentId': '1532475761552597', 'id': 'Y29tbWVudDo0MzYwMTEyNTMwODY3NzU3XzE1MzI0NzU3NjE1NTI1OTc=', 'feedbackId': 'ZmVlZGJhY2s6NDM2MDExMjUzMDg2Nzc1N18xNTMyNDc1NzYxNTUyNTk3', 'date': '2026-06-02T18:39:17.000Z', 'text': 'Oralia orania odilia osneli Olivia oliva Osmani olimpia olimpa Odalis', 'author': {'__typename':</t>
         </is>
@@ -4941,10 +5011,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>46174.64673611111</v>
@@ -5050,13 +5120,13 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="E3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
